--- a/StyleOfDelivery/BCIO-style-hierarchy.xlsx
+++ b/StyleOfDelivery/BCIO-style-hierarchy.xlsx
@@ -442,32 +442,32 @@
       </c>
       <c r="L1" t="inlineStr">
         <is>
+          <t>subontology</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>informaldefinition</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>examples</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
           <t>comment</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>informaldefinition</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>synonyms</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>subontology</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>crossreference</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>examples</t>
         </is>
       </c>
     </row>
@@ -567,7 +567,7 @@
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
-          <t>b is a generically dependent continuant = Def. b is a continuant that g-depends_on one or more other entities. (axiom label in BFO2 Reference: [074-001])</t>
+          <t>A continuant that is dependent on one or other independent continuant bearers. For every instance of A requires some instance of (an independent continuant type) B but which instance of B serves can change from time to time.</t>
         </is>
       </c>
     </row>
@@ -620,12 +620,12 @@
           <t>An &lt;information content entity&gt; transmitted from a communication source to a communication recipient.</t>
         </is>
       </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr"/>
       <c r="Q7" t="inlineStr"/>
     </row>
@@ -703,12 +703,12 @@
           <t>A &lt;material entity&gt; that originates a communication.</t>
         </is>
       </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr"/>
       <c r="Q10" t="inlineStr"/>
     </row>
@@ -786,12 +786,12 @@
           <t>A &lt;person&gt; who receives a communication.</t>
         </is>
       </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr"/>
       <c r="Q13" t="inlineStr"/>
     </row>
@@ -841,14 +841,14 @@
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
-          <t>An occurrent that has temporal proper parts and for some time t, p s-depends_on some material entity at t.</t>
+          <t>p is a process = Def. p is an occurrent that has temporal proper parts and for some time t, p s-depends_on some material entity at t. (axiom label in BFO2 Reference: [083-003])</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>BFO:0000144</t>
+          <t>BCIO:050552</t>
         </is>
       </c>
       <c r="B16" t="inlineStr"/>
@@ -856,7 +856,7 @@
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>process profile</t>
+          <t>communication channel</t>
         </is>
       </c>
       <c r="F16" t="inlineStr"/>
@@ -866,218 +866,242 @@
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
-          <t>b is a process_profile =Def. there is some process c such that b process_profile_of c (axiom label in BFO2 Reference: [093-002])</t>
-        </is>
-      </c>
+          <t>A &lt;process&gt; by which a communication is delivered.</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>BCIO:043000</t>
+          <t>BCIO:050384</t>
         </is>
       </c>
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>process attribute</t>
-        </is>
-      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>communication</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
-          <t>A process profile that is an attribute of a process.</t>
-        </is>
-      </c>
+          <t>A process involving the transmission of information between two or more participants.</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>The participants in the communication process can be of a variety of types, e.g. a human talking to an automated chatbot system, two computer systems exchanging information, a person talking to a pet animal etc.</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>BCIO:044003</t>
+          <t>BCIO:044047</t>
         </is>
       </c>
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>communication process attribute</t>
-        </is>
-      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>communication using commands</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
-          <t>An attribute of a communication process.</t>
+          <t>A communication using statements that order or direct a person to think or behave in a certain way.</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Communication processes can have a variety of attributes, such as their speed, how they are delivered, what language they take place in and the tone of voice in which they occur.  All these types of attributes and more are captured by "communication process attribute"</t>
+          <t>style of delivery</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="P18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>communication using imperatives</t>
+        </is>
+      </c>
       <c r="Q18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>BCIO:044129</t>
+          <t>BCIO:044010</t>
         </is>
       </c>
       <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>affirming communication</t>
+        </is>
+      </c>
       <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>object layout</t>
-        </is>
-      </c>
+      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
-          <t>An attribute of an object used in communication process, concerning how the object's components are arranged.</t>
+          <t>A communication involving acknowledging another's strength or resilience in a given context or situation.</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>the arrangement of components can be deliberately chosen to help communicate intervention content</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>Making explicit statements of partnership or support; Shows approval;</t>
         </is>
       </c>
       <c r="P19" t="inlineStr"/>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>arrangement of chairs in the room for a group intervention, amount of space between blocks of text in a leaflet, arrangement of sections of a website</t>
-        </is>
-      </c>
+      <c r="Q19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>BCIO:044128</t>
+          <t>BCIO:044048</t>
         </is>
       </c>
       <c r="B20" t="inlineStr"/>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>communication using deliberate pauses</t>
+        </is>
+      </c>
       <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>source visual style</t>
-        </is>
-      </c>
+      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
-          <t>An attribute of an intervention person source concerning how they appear to others.</t>
+          <t>A communication in which the speaker purposely leaves gaps between or after their speech utterances.</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>may be purposefully chosen to convey certain attributes of the source</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>staying silent (where this is intended to give others the chance to speak)</t>
+        </is>
+      </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>style of delivery</t>
+          <t>Pauses may be deliberately left to provide opportunities for others to speak or reflect, or to demonstrate non-directiveness.</t>
         </is>
       </c>
       <c r="P20" t="inlineStr"/>
-      <c r="Q20" t="inlineStr">
-        <is>
-          <t>Health care professionals' uniform to convey authority and knowledge, doctors not wearing white coats to speak to children</t>
-        </is>
-      </c>
+      <c r="Q20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>BCIO:044125</t>
+          <t>BCIO:044011</t>
         </is>
       </c>
       <c r="B21" t="inlineStr"/>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>agenda-sharing communication</t>
+        </is>
+      </c>
       <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>tone of voice</t>
-        </is>
-      </c>
+      <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
-          <t>An attribute of an oral communication relating to the rhythm and pitch of what is said.</t>
+          <t>A communication in which the initiator and one or more activity participants work together to determine a focus for the activity to be undertaken.</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>agenda mapping</t>
+        </is>
+      </c>
       <c r="Q21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>BCIO:044004</t>
+          <t>BCIO:044036</t>
         </is>
       </c>
       <c r="B22" t="inlineStr"/>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>communication involving acceptance that recipients views may be different to the initiator's views</t>
+        </is>
+      </c>
       <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>communication style</t>
-        </is>
-      </c>
+      <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
         <is>
-          <t>A particular manner of communicating aimed at inducing or avoiding certain kinds of responses in others, or demonstrating certain characteristics of the initiator.</t>
+          <t>A communication involving accepting that the recipient has different beliefs to the initiator and continuing with the planned activities while allowing both views to exist.</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr">
         <is>
-          <t>style of delivery</t>
+          <t>From Motivational Interviewing</t>
         </is>
       </c>
       <c r="P22" t="inlineStr"/>
@@ -1086,78 +1110,68 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>BCIO:044083</t>
+          <t>BCIO:044024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr"/>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>communication avoiding argumentation</t>
+        </is>
+      </c>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>attentive communication style</t>
-        </is>
-      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
-          <t>A communication style characterised by purposeful consideration of another's statements.</t>
+          <t>A communication which aims to focus on the feelings of others without debating the truth or falsity of statements or ideas.</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>This involves communicating in a manner that ensures the recipient knows that they are being heard</t>
+          <t>style of delivery</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr"/>
-      <c r="Q23" t="inlineStr">
-        <is>
-          <t>"listened carefully to what you had to say"</t>
-        </is>
-      </c>
+      <c r="Q23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>BCIO:044005</t>
+          <t>BCIO:044124</t>
         </is>
       </c>
       <c r="B24" t="inlineStr"/>
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>relationship building</t>
+        </is>
+      </c>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>intervention style of delivery</t>
-        </is>
-      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
         <is>
-          <t>A communication style that is an attribute of an intervention content communication process.</t>
+          <t>A communication aimed at building or managing aspects of the interpersonal relationship between an initiator and a recipient rather than focusing on delivering communication content.</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>when a communication style is used as part of an intervention content communication process, then it qualifies as an intervention style of delivery</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>offering contact, inviting patient to contact you in the event of difficulties or questions</t>
         </is>
       </c>
       <c r="P24" t="inlineStr"/>
@@ -1166,236 +1180,219 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>BCIO:044099</t>
+          <t>BCIO:044028</t>
         </is>
       </c>
       <c r="B25" t="inlineStr"/>
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr"/>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>communication encouraging discussion</t>
+        </is>
+      </c>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>directive communication style</t>
-        </is>
-      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
-          <t>A communication style intended to play an active role in another person's decision making.</t>
+          <t>A communication in which the initiator promotes an extended two-way discussion regarding a topic.</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>Note that this class is different from direct communication style</t>
+          <t>style of delivery</t>
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
       <c r="O25" t="inlineStr">
         <is>
-          <t>style of delivery</t>
+          <t>Contrasts with a more one-way, didactic style</t>
         </is>
       </c>
       <c r="P25" t="inlineStr"/>
-      <c r="Q25" t="inlineStr">
-        <is>
-          <t>http://purl.bioontology.org/ontology/MESH/D037001</t>
-        </is>
-      </c>
+      <c r="Q25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>BCIO:044106</t>
+          <t>BCIO:044029</t>
         </is>
       </c>
       <c r="B26" t="inlineStr"/>
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>communication evoking another's ideas about change</t>
+        </is>
+      </c>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>informal communication style</t>
-        </is>
-      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr">
         <is>
-          <t>A communication style characterised by the use of casual or colloquial language rather than formal language.</t>
+          <t>A communication in which the initiator attempts to elicit the recipient’s own thoughts and ideas about change rather than imposing the initiator’s own opinion.</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>"Colloquial" language is language that is typically used in ordinary conversation rather than in formal communication</t>
+          <t>style of delivery</t>
         </is>
       </c>
       <c r="N26" t="inlineStr"/>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="P26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>evoking change talk in motivational interviewing</t>
+        </is>
+      </c>
       <c r="Q26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>BCIO:044089</t>
+          <t>BCIO:044041</t>
         </is>
       </c>
       <c r="B27" t="inlineStr"/>
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr"/>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>communication offering choice</t>
+        </is>
+      </c>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>communication style conveying concern</t>
-        </is>
-      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr">
         <is>
-          <t>A communication style demonstrating one perceives an unwanted circumstance for the recipient.</t>
+          <t>A communication involving the initiator offering a range of options to the recipient.</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
         </is>
       </c>
       <c r="N27" t="inlineStr"/>
-      <c r="O27" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr"/>
       <c r="Q27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>BCIO:044100</t>
+          <t>BCIO:044026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr"/>
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>communication checking for others' understanding</t>
+        </is>
+      </c>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>easily comprehended communication style</t>
-        </is>
-      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr">
         <is>
-          <t>A communication style characterised by using language in a manner intended to be easily understandable to a recipient.</t>
+          <t>A communication in which the instigator asks questions to determine if the recipient has comprehended information that has been presented.</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>This can involve using plain and simple language</t>
+          <t>style of delivery</t>
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
-      <c r="O28" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr"/>
-      <c r="Q28" t="inlineStr">
-        <is>
-          <t>using non-technical language, using clear language, avoiding jargon</t>
-        </is>
-      </c>
+      <c r="Q28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>BCIO:044119</t>
+          <t>BCIO:044077</t>
         </is>
       </c>
       <c r="B29" t="inlineStr"/>
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>script-based communication</t>
+        </is>
+      </c>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>semi-structured communication style</t>
-        </is>
-      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr">
         <is>
-          <t>A communication style involving the communication content having some constituent pre-planned parts but also being responsive to inputs.</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>organised communication style</t>
-        </is>
-      </c>
+          <t>A communication which follows a pre-written sequence of instructions that are interpreted or carried out by a person or by a program.</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="O29" t="inlineStr">
         <is>
-          <t>style of delivery</t>
+          <t>This class involves tightly following a set of written instructions. It is different to structured communication style, which is a pre-planned style but not to the extent of using a written script.</t>
         </is>
       </c>
       <c r="P29" t="inlineStr"/>
-      <c r="Q29" t="inlineStr">
-        <is>
-          <t>Using talking points, using conversation guides, having a list of topics to cover</t>
-        </is>
-      </c>
+      <c r="Q29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>BCIO:044085</t>
+          <t>BCIO:044050</t>
         </is>
       </c>
       <c r="B30" t="inlineStr"/>
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr"/>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>communication using particular language</t>
+        </is>
+      </c>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>collaborative communication style</t>
-        </is>
-      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr">
         <is>
-          <t>A communication style characterised by a sense of the initiator and recipient working together, the initiator showing sensitivity to the others' needs, in order to obtain an outcome desired by all.</t>
+          <t>A communication using certain vocabulary or phraseology.</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
         </is>
       </c>
       <c r="N30" t="inlineStr"/>
-      <c r="O30" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr"/>
       <c r="Q30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>BCIO:044087</t>
+          <t>BCIO:044056</t>
         </is>
       </c>
       <c r="B31" t="inlineStr"/>
@@ -1403,32 +1400,32 @@
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>communication using selected words from a second language</t>
+        </is>
+      </c>
       <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>communication style conveying acceptance</t>
-        </is>
-      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr">
         <is>
-          <t>A communication style that conveys respect and regard for the recipient as an individual.</t>
+          <t>A communication using occasional words chosen from a language spoken by both the instigator and the recipient that is not the main language.</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
-      <c r="O31" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr"/>
       <c r="Q31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>BCIO:044121</t>
+          <t>BCIO:044052</t>
         </is>
       </c>
       <c r="B32" t="inlineStr"/>
@@ -1436,32 +1433,32 @@
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>communication using non-pressurising language</t>
+        </is>
+      </c>
       <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>theatrical communication style</t>
-        </is>
-      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr">
         <is>
-          <t>A communication style similar to that used for dramatic performance or the theatre.</t>
+          <t>A communication using language chosen to avoid coercing or persuading the recipient to think, feel or behave in a certain manner.</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
         </is>
       </c>
       <c r="N32" t="inlineStr"/>
-      <c r="O32" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr"/>
       <c r="Q32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>BCIO:044107</t>
+          <t>BCIO:044053</t>
         </is>
       </c>
       <c r="B33" t="inlineStr"/>
@@ -1469,32 +1466,32 @@
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>communication using slang</t>
+        </is>
+      </c>
       <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>intellectual communication style</t>
-        </is>
-      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr">
         <is>
-          <t>A communication style characterised by an emphasis on reasoning and promoting objective understanding.</t>
+          <t>A communication using informal language shared by members of a particular community.</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr"/>
       <c r="Q33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>BCIO:050380</t>
+          <t>BCIO:044051</t>
         </is>
       </c>
       <c r="B34" t="inlineStr"/>
@@ -1502,32 +1499,32 @@
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr"/>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>communication using neutral language</t>
+        </is>
+      </c>
       <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>aggressive communication style</t>
-        </is>
-      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr">
         <is>
-          <t>A communication style characterised by aggression.</t>
+          <t>A communication using language in a manner which does not demonstrate an opinion on a particular issue.</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
         </is>
       </c>
       <c r="N34" t="inlineStr"/>
-      <c r="O34" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr"/>
       <c r="Q34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>BCIO:044110</t>
+          <t>BCIO:044055</t>
         </is>
       </c>
       <c r="B35" t="inlineStr"/>
@@ -1535,32 +1532,32 @@
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr"/>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>communication avoiding offensive language</t>
+        </is>
+      </c>
       <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>non-defensive communication style</t>
-        </is>
-      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr">
         <is>
-          <t>A communication style characterised by suggesting the initiator is open to or able to accept criticism.</t>
+          <t>A communication using language chosen by the instigator to avoid using words or phrases that could be perceived as rude or insulting.</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
         </is>
       </c>
       <c r="N35" t="inlineStr"/>
-      <c r="O35" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr"/>
       <c r="Q35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>BCIO:044116</t>
+          <t>BCIO:044054</t>
         </is>
       </c>
       <c r="B36" t="inlineStr"/>
@@ -1568,78 +1565,78 @@
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr"/>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>communication using specialist language</t>
+        </is>
+      </c>
       <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>relaxed communication style</t>
-        </is>
-      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr">
         <is>
-          <t>A communication style characterised by a lack of tension or anxiety.</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>calm communication style</t>
-        </is>
-      </c>
-      <c r="O36" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="P36" t="inlineStr"/>
+          <t>A communication using words or expressions used by a profession or group that are difficult for others not in that profession or group to understand.</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>using jargon</t>
+        </is>
+      </c>
       <c r="Q36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>BCIO:044117</t>
+          <t>BCIO:044030</t>
         </is>
       </c>
       <c r="B37" t="inlineStr"/>
       <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr"/>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>exploring communication</t>
+        </is>
+      </c>
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>respectful communication style</t>
-        </is>
-      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr">
         <is>
-          <t>A communication style suggesting an understanding of and regard for the feelings, wishes, or rights of others.</t>
+          <t>A communication to better understand what a person thinks or feels about a topic or an experience.</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>This class involves showing regard for the feelings etc of others from the outset, but not necessarily adapting one's own communication based on what the other says.  In contrast, responsive communication style is adapting the response as a result of how another person is communicating.</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr"/>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>eliciting or seeking information</t>
+        </is>
+      </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>style of delivery</t>
+          <t>This can include asking questions or prompting elaboration e.g 'Tell me more about that'</t>
         </is>
       </c>
       <c r="P37" t="inlineStr"/>
-      <c r="Q37" t="inlineStr">
-        <is>
-          <t>"acknowledging the victim's feelings"</t>
-        </is>
-      </c>
+      <c r="Q37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>BCIO:044112</t>
+          <t>BCIO:050387</t>
         </is>
       </c>
       <c r="B38" t="inlineStr"/>
@@ -1647,23 +1644,28 @@
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr"/>
-      <c r="G38" t="inlineStr"/>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>communication exploring a person's thoughts about an experience</t>
+        </is>
+      </c>
       <c r="H38" t="inlineStr"/>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>non-judgmental communication style</t>
-        </is>
-      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr">
         <is>
-          <t>A communication style that demonstrates that one is not assigning a positive or negative valence to another's views or behaviours.</t>
+          <t>An exploring communication focused on what a person thinks about an experience.</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
         </is>
       </c>
       <c r="N38" t="inlineStr"/>
       <c r="O38" t="inlineStr">
         <is>
-          <t>style of delivery</t>
+          <t>An experience can be any situation or state a person encounters or undergoes</t>
         </is>
       </c>
       <c r="P38" t="inlineStr"/>
@@ -1672,7 +1674,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>BCIO:044104</t>
+          <t>BCIO:050383</t>
         </is>
       </c>
       <c r="B39" t="inlineStr"/>
@@ -1680,23 +1682,27 @@
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr"/>
-      <c r="G39" t="inlineStr"/>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>communication exploring a person's feelings about a topic</t>
+        </is>
+      </c>
       <c r="H39" t="inlineStr"/>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>formal communication style</t>
-        </is>
-      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr">
         <is>
-          <t>A communication style characterised by the use of traditional standards of correctness and etiquette and without casual, contracted, or colloquial forms of language.</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr"/>
-      <c r="O39" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
+          <t>An exploring communication focused on a person's affective responses to a matter.</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>Elicit concerns, problems and reactions</t>
         </is>
       </c>
       <c r="P39" t="inlineStr"/>
@@ -1705,7 +1711,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>BCIO:044108</t>
+          <t>BCIO:050385</t>
         </is>
       </c>
       <c r="B40" t="inlineStr"/>
@@ -1713,36 +1719,37 @@
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr"/>
-      <c r="G40" t="inlineStr"/>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>communication exploring a person's feelings about an experience</t>
+        </is>
+      </c>
       <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>interactive communication style</t>
-        </is>
-      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr">
         <is>
-          <t>A communication style characterised by being responsive to the recipient's activity.</t>
+          <t>An exploring communication focused on a person's affective responses to an experience.</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
         </is>
       </c>
       <c r="N40" t="inlineStr"/>
       <c r="O40" t="inlineStr">
         <is>
-          <t>style of delivery</t>
+          <t>An experience can be any situation or state a person encounters or undergoes</t>
         </is>
       </c>
       <c r="P40" t="inlineStr"/>
-      <c r="Q40" t="inlineStr">
-        <is>
-          <t>interactive presentation</t>
-        </is>
-      </c>
+      <c r="Q40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>BCIO:044114</t>
+          <t>BCIO:050386</t>
         </is>
       </c>
       <c r="B41" t="inlineStr"/>
@@ -1750,23 +1757,27 @@
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr"/>
-      <c r="G41" t="inlineStr"/>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>communication exploring a person's thoughts about a topic</t>
+        </is>
+      </c>
       <c r="H41" t="inlineStr"/>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>persuasive communication style</t>
-        </is>
-      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr">
         <is>
-          <t>A communication style which aims to induce or urge the adoption of certain beliefs, theories or lines of action.</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr"/>
-      <c r="O41" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
+          <t>An exploring communication focused on what a person thinks about a matter.</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>clarifying what someone has said</t>
         </is>
       </c>
       <c r="P41" t="inlineStr"/>
@@ -1775,40 +1786,40 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>BCIO:044111</t>
+          <t>BCIO:044071</t>
         </is>
       </c>
       <c r="B42" t="inlineStr"/>
       <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr"/>
-      <c r="F42" t="inlineStr"/>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>reflective communication</t>
+        </is>
+      </c>
       <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr"/>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>non-confrontational communication style</t>
-        </is>
-      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr">
         <is>
-          <t>A communication style characterised by being diplomatic and avoiding conflict.</t>
+          <t>A communication presenting a person's previously expressed thoughts and feelings back to them.</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
         </is>
       </c>
       <c r="N42" t="inlineStr"/>
-      <c r="O42" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr"/>
       <c r="Q42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>BCIO:044102</t>
+          <t>BCIO:044075</t>
         </is>
       </c>
       <c r="B43" t="inlineStr"/>
@@ -1816,32 +1827,36 @@
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr"/>
-      <c r="G43" t="inlineStr"/>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>emotion-emphasising reflective communication</t>
+        </is>
+      </c>
       <c r="H43" t="inlineStr"/>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>engaging communication style</t>
-        </is>
-      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr">
         <is>
-          <t>A communication style characterised by attempting to attract and maintain a recipient's interest or attention.</t>
+          <t>A reflective communication highlighting the emotional aspects of an issue as previously described by the recipient.</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
         </is>
       </c>
       <c r="N43" t="inlineStr"/>
-      <c r="O43" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="P43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>"reflection of feeling" in Motivational Interviewing</t>
+        </is>
+      </c>
       <c r="Q43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>BCIO:044079</t>
+          <t>BCIO:044073</t>
         </is>
       </c>
       <c r="B44" t="inlineStr"/>
@@ -1849,32 +1864,36 @@
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr"/>
-      <c r="G44" t="inlineStr"/>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>double-sided reflective communication</t>
+        </is>
+      </c>
       <c r="H44" t="inlineStr"/>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>active participation encouraging communication style</t>
-        </is>
-      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr">
         <is>
-          <t>A communication style marked by fostering the involvement of the recipient as an engaged actor in the activity to be undertaken rather than as a passive recipient.</t>
+          <t>A reflective communication in which the instigator aims to highlight both the positive and negative sides of an issue as previously expressed by the recipient.</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
         </is>
       </c>
       <c r="N44" t="inlineStr"/>
-      <c r="O44" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="P44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>"double-sided reflection" in Motivational Interviewing</t>
+        </is>
+      </c>
       <c r="Q44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>BCIO:044091</t>
+          <t>BCIO:044074</t>
         </is>
       </c>
       <c r="B45" t="inlineStr"/>
@@ -1882,36 +1901,36 @@
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr"/>
-      <c r="G45" t="inlineStr"/>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>metaphor-using reflective communication</t>
+        </is>
+      </c>
       <c r="H45" t="inlineStr"/>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>communication style conveying hopefulness</t>
-        </is>
-      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr">
         <is>
-          <t>A communication style which imparts a feeling of optimism that a person will attain a desired outcome.</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr">
-        <is>
-          <t>optimism, positivity</t>
-        </is>
-      </c>
-      <c r="O45" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="P45" t="inlineStr"/>
+          <t>A reflective communication in which the instigator  replaces a word or phrase of the recipient's prior assertion with a figure of speech suggesting an analogy.</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>"metaphorical reflection" in Motivational Interviewing</t>
+        </is>
+      </c>
       <c r="Q45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>BCIO:050391</t>
+          <t>BCIO:044076</t>
         </is>
       </c>
       <c r="B46" t="inlineStr"/>
@@ -1919,32 +1938,36 @@
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr"/>
-      <c r="G46" t="inlineStr"/>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>re-evaluation prompting reflective communication</t>
+        </is>
+      </c>
       <c r="H46" t="inlineStr"/>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>non-responsive communication style</t>
-        </is>
-      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr">
         <is>
-          <t>A communication style characterised by not adapting to the views and behaviours of the recipient.</t>
+          <t>A reflective communication in which the instigator restates the recipient's prior assertation in a less credible way to prompt reconsideration of the assertion.</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
         </is>
       </c>
       <c r="N46" t="inlineStr"/>
-      <c r="O46" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="P46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>"amplified reflection" in Motivational Interviewing</t>
+        </is>
+      </c>
       <c r="Q46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>BCIO:044094</t>
+          <t>BCIO:044072</t>
         </is>
       </c>
       <c r="B47" t="inlineStr"/>
@@ -1952,65 +1975,69 @@
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr"/>
-      <c r="G47" t="inlineStr"/>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>summarising reflective communication</t>
+        </is>
+      </c>
       <c r="H47" t="inlineStr"/>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>communication style conveying support for change</t>
-        </is>
-      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr">
         <is>
-          <t>A communication style which imparts one's belief that the recipient can change.</t>
+          <t>A reflective communication in which the instigator pulls together key points from a complex story told by the recipient in a succinct restatement.</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
         </is>
       </c>
       <c r="N47" t="inlineStr"/>
-      <c r="O47" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="P47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>"summarising reflection" in Motivational Interviewing</t>
+        </is>
+      </c>
       <c r="Q47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>BCIO:044122</t>
+          <t>BCIO:044012</t>
         </is>
       </c>
       <c r="B48" t="inlineStr"/>
       <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr"/>
-      <c r="F48" t="inlineStr"/>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>asking questions</t>
+        </is>
+      </c>
       <c r="G48" t="inlineStr"/>
       <c r="H48" t="inlineStr"/>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>verbally dominant communication style</t>
-        </is>
-      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr">
         <is>
-          <t>A communication style characterised by one participant having more control over a conversation than the other.</t>
+          <t>A communication in which some participant requests information from another participant.</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
         </is>
       </c>
       <c r="N48" t="inlineStr"/>
-      <c r="O48" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr"/>
       <c r="Q48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>BCIO:050389</t>
+          <t>BCIO:044013</t>
         </is>
       </c>
       <c r="B49" t="inlineStr"/>
@@ -2018,37 +2045,32 @@
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr"/>
-      <c r="G49" t="inlineStr"/>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>asking closed-ended questions</t>
+        </is>
+      </c>
       <c r="H49" t="inlineStr"/>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>direct communication style</t>
-        </is>
-      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr">
         <is>
-          <t>A communication style characterised by the explicit presentation of information.</t>
+          <t>Asking questions that can only be answered with a limited set of responses.</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>Note that this class is different from directive communication style</t>
+          <t>style of delivery</t>
         </is>
       </c>
       <c r="N49" t="inlineStr"/>
-      <c r="O49" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr"/>
       <c r="Q49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>BCIO:044105</t>
+          <t>BCIO:044016</t>
         </is>
       </c>
       <c r="B50" t="inlineStr"/>
@@ -2056,32 +2078,32 @@
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr"/>
-      <c r="G50" t="inlineStr"/>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>asking open-ended questions</t>
+        </is>
+      </c>
       <c r="H50" t="inlineStr"/>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>impatient communication style</t>
-        </is>
-      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr">
         <is>
-          <t>A communication style conveying feelings of annoyance at time taken to understand or complete a process.</t>
+          <t>Asking questions that cannot be answered with a simple yes or no, but instead require the questionee to elaborate on their points.</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
         </is>
       </c>
       <c r="N50" t="inlineStr"/>
-      <c r="O50" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr"/>
       <c r="Q50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>BCIO:044131</t>
+          <t>BCIO:050382</t>
         </is>
       </c>
       <c r="B51" t="inlineStr"/>
@@ -2089,32 +2111,32 @@
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr"/>
-      <c r="G51" t="inlineStr"/>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>asking clarifying questions</t>
+        </is>
+      </c>
       <c r="H51" t="inlineStr"/>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>anxious communication style</t>
-        </is>
-      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr">
         <is>
-          <t>A communication style characterised by nervousness or unease.</t>
+          <t>Asking questions in order to better understand an issue.</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
         </is>
       </c>
       <c r="N51" t="inlineStr"/>
-      <c r="O51" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr"/>
       <c r="Q51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>BCIO:044084</t>
+          <t>BCIO:044015</t>
         </is>
       </c>
       <c r="B52" t="inlineStr"/>
@@ -2122,41 +2144,36 @@
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr"/>
-      <c r="G52" t="inlineStr"/>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>asking leading questions</t>
+        </is>
+      </c>
       <c r="H52" t="inlineStr"/>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>autonomy-supportive communication style</t>
-        </is>
-      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr">
         <is>
-          <t>A communication style which aims to promote the recipient's capacity to make their own decisions.</t>
+          <t>Asking questions designed to prompt the questionee to answer in a specific, pre-determined manner.</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>from Self-Determination Theory interventions.</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr">
-        <is>
-          <t>needs-supportive communication style</t>
-        </is>
-      </c>
-      <c r="O52" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="P52" t="inlineStr"/>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>asking directive questions</t>
+        </is>
+      </c>
       <c r="Q52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>BCIO:044086</t>
+          <t>BCIO:044014</t>
         </is>
       </c>
       <c r="B53" t="inlineStr"/>
@@ -2164,173 +2181,164 @@
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr"/>
-      <c r="G53" t="inlineStr"/>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>asking focused questions</t>
+        </is>
+      </c>
       <c r="H53" t="inlineStr"/>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>cold communication style</t>
-        </is>
-      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr">
         <is>
-          <t>A communication style suggesting a lack of human interest or friendliness towards the recipient.</t>
+          <t>Asking questions designed to narrow discussion to focus on a particular aspect or topic.</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
         </is>
       </c>
       <c r="N53" t="inlineStr"/>
-      <c r="O53" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr"/>
       <c r="Q53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>BCIO:044098</t>
+          <t>BCIO:044062</t>
         </is>
       </c>
       <c r="B54" t="inlineStr"/>
       <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr"/>
-      <c r="F54" t="inlineStr"/>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>communication avoiding interrupting</t>
+        </is>
+      </c>
       <c r="G54" t="inlineStr"/>
       <c r="H54" t="inlineStr"/>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>didactic communication style</t>
-        </is>
-      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr">
         <is>
-          <t>A communication style characterised by the initiator addressing the recipient in the manner of a teacher or lecturer.</t>
+          <t>A communication in which at least one participant endeavours to not interject before another participant has finished making their point.</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
         </is>
       </c>
       <c r="N54" t="inlineStr"/>
-      <c r="O54" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
       <c r="P54" t="inlineStr"/>
-      <c r="Q54" t="inlineStr">
-        <is>
-          <t>gave a short lecture, conference presentation</t>
-        </is>
-      </c>
+      <c r="Q54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>BCIO:044095</t>
+          <t>BCIO:044022</t>
         </is>
       </c>
       <c r="B55" t="inlineStr"/>
       <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr"/>
-      <c r="F55" t="inlineStr"/>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>communication adding intensity to another's views</t>
+        </is>
+      </c>
       <c r="G55" t="inlineStr"/>
       <c r="H55" t="inlineStr"/>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>communication style demonstrating positive regard</t>
-        </is>
-      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr">
         <is>
-          <t>A communication style demonstrating acceptance of everything about the recipient.</t>
+          <t>A communication using statements that add intensity to the content or emotion expressed by another person.</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
         </is>
       </c>
       <c r="N55" t="inlineStr"/>
-      <c r="O55" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="P55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>"overshooting" in motivational interviewing</t>
+        </is>
+      </c>
       <c r="Q55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>BCIO:044118</t>
+          <t>BCIO:044040</t>
         </is>
       </c>
       <c r="B56" t="inlineStr"/>
       <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr"/>
-      <c r="F56" t="inlineStr"/>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>communication involving elaboration of arguments</t>
+        </is>
+      </c>
       <c r="G56" t="inlineStr"/>
       <c r="H56" t="inlineStr"/>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>responsive communication style</t>
-        </is>
-      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr">
         <is>
-          <t>A communication style characterised by adapting to the views and behaviours of the recipient.</t>
+          <t>A communication further developing a declarative statement that has been made  by making it clearer, more precise, bringing out its consequences or giving a concrete example.</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>This class is adapting response as a result of how another person is communicating. In contrast, respectful communication style involves showing regard for the feelings etc of others from the outset, but not necessarily adapting one's own communication based on what the other says</t>
+          <t>style of delivery</t>
         </is>
       </c>
       <c r="N56" t="inlineStr"/>
-      <c r="O56" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
       <c r="P56" t="inlineStr"/>
       <c r="Q56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>BCIO:044120</t>
+          <t>BCIO:044070</t>
         </is>
       </c>
       <c r="B57" t="inlineStr"/>
       <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr"/>
-      <c r="F57" t="inlineStr"/>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>paraphrasing</t>
+        </is>
+      </c>
       <c r="G57" t="inlineStr"/>
       <c r="H57" t="inlineStr"/>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>structured communication style</t>
-        </is>
-      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr">
         <is>
-          <t>A communication style involving the communication content having constituent pre-planned parts.</t>
+          <t>A communication in which one participant summarises what the other said.</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>This class is pre-planned style but not to the extent of using a written script. In contrast, "Script-based communication" involves tightly following a set of written instructions.</t>
-        </is>
-      </c>
-      <c r="N57" t="inlineStr">
-        <is>
-          <t>standardised</t>
-        </is>
-      </c>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr"/>
       <c r="O57" t="inlineStr">
         <is>
-          <t>style of delivery</t>
+          <t>This class is different to "communication involving confirmatory rephrasing" as this class is simply about summarising what another person said.</t>
         </is>
       </c>
       <c r="P57" t="inlineStr"/>
@@ -2339,106 +2347,101 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>BCIO:050381</t>
+          <t>BCIO:044065</t>
         </is>
       </c>
       <c r="B58" t="inlineStr"/>
       <c r="C58" t="inlineStr"/>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr"/>
-      <c r="F58" t="inlineStr"/>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>negotiation</t>
+        </is>
+      </c>
       <c r="G58" t="inlineStr"/>
       <c r="H58" t="inlineStr"/>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>angry communication style</t>
-        </is>
-      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr">
         <is>
-          <t>A communication style characterised by anger.</t>
+          <t>A communication involving goal-oriented collaboration to arrive at an agreement or compromise on a matter of importance to the individuals involved.</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
         </is>
       </c>
       <c r="N58" t="inlineStr"/>
-      <c r="O58" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
       <c r="P58" t="inlineStr"/>
       <c r="Q58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>BCIO:044000</t>
+          <t>BCIO:044058</t>
         </is>
       </c>
       <c r="B59" t="inlineStr"/>
       <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr"/>
-      <c r="F59" t="inlineStr"/>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>communication using rational arguments</t>
+        </is>
+      </c>
       <c r="G59" t="inlineStr"/>
       <c r="H59" t="inlineStr"/>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>behaviour change intervention style of delivery</t>
-        </is>
-      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr">
         <is>
-          <t>A communication style that is an attribute of a BCI content communication process.</t>
+          <t>A communication that involves the use of declarative propositions based on what the communicator believes to be logical.</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>when a communication style is used as part of a BCI content communication process, then it qualifies as a BCI style of delivery</t>
+          <t>style of delivery</t>
         </is>
       </c>
       <c r="N59" t="inlineStr"/>
-      <c r="O59" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
       <c r="P59" t="inlineStr"/>
       <c r="Q59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>BCIO:044082</t>
+          <t>BCIO:044027</t>
         </is>
       </c>
       <c r="B60" t="inlineStr"/>
       <c r="C60" t="inlineStr"/>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr"/>
-      <c r="F60" t="inlineStr"/>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>communication checking for own understanding</t>
+        </is>
+      </c>
       <c r="G60" t="inlineStr"/>
       <c r="H60" t="inlineStr"/>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>articulate communication style</t>
-        </is>
-      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr">
         <is>
-          <t>A communication style characterised by the initiator fluently using language to express ideas.</t>
+          <t>A communication in which the instigator asks questions to determine if they have correctly comprehended the information presented by another.</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>fluent</t>
-        </is>
-      </c>
-      <c r="O60" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
+          <t>clarifying what another has said</t>
         </is>
       </c>
       <c r="P60" t="inlineStr"/>
@@ -2447,72 +2450,72 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>BCIO:044103</t>
+          <t>BCIO:044039</t>
         </is>
       </c>
       <c r="B61" t="inlineStr"/>
       <c r="C61" t="inlineStr"/>
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr"/>
-      <c r="F61" t="inlineStr"/>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>communication involving confirmatory rephrasing</t>
+        </is>
+      </c>
       <c r="G61" t="inlineStr"/>
       <c r="H61" t="inlineStr"/>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>entertaining communication style</t>
-        </is>
-      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr">
         <is>
-          <t>A communication style intended to be amusing or enjoyable for the recipient.</t>
-        </is>
-      </c>
-      <c r="N61" t="inlineStr">
-        <is>
-          <t>fun</t>
-        </is>
-      </c>
-      <c r="O61" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="P61" t="inlineStr"/>
+          <t>A communication involving the initiator rephrasing what a recipient says in a manner intended to confirm understanding of the recipient's situation rather than confront.</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>"coming alongside" in Motivational Interviewing</t>
+        </is>
+      </c>
       <c r="Q61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>BCIO:044101</t>
+          <t>BCIO:044060</t>
         </is>
       </c>
       <c r="B62" t="inlineStr"/>
       <c r="C62" t="inlineStr"/>
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr"/>
-      <c r="F62" t="inlineStr"/>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>guiding communication</t>
+        </is>
+      </c>
       <c r="G62" t="inlineStr"/>
       <c r="H62" t="inlineStr"/>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>empathic communication style</t>
-        </is>
-      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr">
         <is>
-          <t>A communication style which conveys an insightful awareness of the feelings and behaviours of the recipient.</t>
+          <t>A communication that involves suggesting adoption of certain beliefs, theories or lines of action by others.</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>sensitivity, compassion</t>
-        </is>
-      </c>
-      <c r="O62" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
+          <t>When a practitioner suggests to a patient 'Could you think about it like this...'</t>
         </is>
       </c>
       <c r="P62" t="inlineStr"/>
@@ -2521,73 +2524,73 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>BCIO:044109</t>
+          <t>BCIO:044035</t>
         </is>
       </c>
       <c r="B63" t="inlineStr"/>
       <c r="C63" t="inlineStr"/>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr"/>
-      <c r="F63" t="inlineStr"/>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>communication inviting reactions to content presented</t>
+        </is>
+      </c>
       <c r="G63" t="inlineStr"/>
       <c r="H63" t="inlineStr"/>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>legitimising communication style</t>
-        </is>
-      </c>
+      <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr">
         <is>
-          <t>A communication style characterised by making a person feel that their perspective or emotions are legitimate.</t>
+          <t>A communication seeking information about a person's responses to the  content presented.</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>This entails a deliberate strategy to make the person feel their perspective is legitimate</t>
-        </is>
-      </c>
-      <c r="N63" t="inlineStr">
-        <is>
-          <t>validating emotions</t>
-        </is>
-      </c>
-      <c r="O63" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="P63" t="inlineStr"/>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>asking for opinions</t>
+        </is>
+      </c>
       <c r="Q63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>BCIO:044115</t>
+          <t>BCIO:044043</t>
         </is>
       </c>
       <c r="B64" t="inlineStr"/>
       <c r="C64" t="inlineStr"/>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr"/>
-      <c r="F64" t="inlineStr"/>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>communication using a particular form of address</t>
+        </is>
+      </c>
       <c r="G64" t="inlineStr"/>
       <c r="H64" t="inlineStr"/>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>polite communication style</t>
-        </is>
-      </c>
+      <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr">
         <is>
-          <t>A communication style characterised by courtesy.</t>
+          <t>A communication addressing a person using a certain name or title to refer to that person.</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
         </is>
       </c>
       <c r="N64" t="inlineStr"/>
       <c r="O64" t="inlineStr">
         <is>
-          <t>style of delivery</t>
+          <t>The child classes of this class are specific types of address, whereas this class is for a non-specific type of address.</t>
         </is>
       </c>
       <c r="P64" t="inlineStr"/>
@@ -2596,7 +2599,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>BCIO:044092</t>
+          <t>BCIO:044046</t>
         </is>
       </c>
       <c r="B65" t="inlineStr"/>
@@ -2604,23 +2607,27 @@
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr"/>
-      <c r="G65" t="inlineStr"/>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>communication using preferred form of address</t>
+        </is>
+      </c>
       <c r="H65" t="inlineStr"/>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>communication style conveying perceived superiority</t>
-        </is>
-      </c>
+      <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr">
         <is>
-          <t>A communication style which imparts a feeling that the instigator believes themselves to be higher in status than the recipient.</t>
-        </is>
-      </c>
-      <c r="N65" t="inlineStr"/>
-      <c r="O65" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
+          <t>A communication addressing a person using a name or title that the person has specified the instigator should use.</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>Depending on whether Suzie Jones prefers to be addressed formally, or by her given name, saying either "Hello Mrs Jones" or "Hello Suzie"</t>
         </is>
       </c>
       <c r="P65" t="inlineStr"/>
@@ -2629,7 +2636,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>BCIO:050392</t>
+          <t>BCIO:044045</t>
         </is>
       </c>
       <c r="B66" t="inlineStr"/>
@@ -2637,32 +2644,32 @@
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr"/>
-      <c r="G66" t="inlineStr"/>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>communication using informal address</t>
+        </is>
+      </c>
       <c r="H66" t="inlineStr"/>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>rushed communication style</t>
-        </is>
-      </c>
+      <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr">
         <is>
-          <t>A communication style conveying information in a hurried way.</t>
+          <t>A communication addressing a person using a casual or colloquial name or title to refer to that person.</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
         </is>
       </c>
       <c r="N66" t="inlineStr"/>
-      <c r="O66" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
       <c r="P66" t="inlineStr"/>
       <c r="Q66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>BCIO:044113</t>
+          <t>BCIO:044044</t>
         </is>
       </c>
       <c r="B67" t="inlineStr"/>
@@ -2670,60 +2677,60 @@
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr"/>
-      <c r="G67" t="inlineStr"/>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>communication using formal address</t>
+        </is>
+      </c>
       <c r="H67" t="inlineStr"/>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>patient communication style</t>
-        </is>
-      </c>
+      <c r="I67" t="inlineStr"/>
       <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr">
         <is>
-          <t>A communication style conveying willingness to take time to understand or complete a process.</t>
+          <t>A communication addressing a person using a formal, legal or official name or title to refer to that person.</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
         </is>
       </c>
       <c r="N67" t="inlineStr"/>
-      <c r="O67" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
       <c r="P67" t="inlineStr"/>
-      <c r="Q67" t="inlineStr">
-        <is>
-          <t>"willing to listen"</t>
-        </is>
-      </c>
+      <c r="Q67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>BCIO:050390</t>
+          <t>BCIO:044023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr"/>
       <c r="C68" t="inlineStr"/>
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr"/>
-      <c r="F68" t="inlineStr"/>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>communication asking permission to provide information and advice</t>
+        </is>
+      </c>
       <c r="G68" t="inlineStr"/>
       <c r="H68" t="inlineStr"/>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>humorous communication style</t>
-        </is>
-      </c>
+      <c r="I68" t="inlineStr"/>
       <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr">
         <is>
-          <t>A communication style intended to amuse.</t>
-        </is>
-      </c>
-      <c r="N68" t="inlineStr"/>
-      <c r="O68" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
+          <t>A communication which involves asking for approval before sharing knowledge and giving guidance.</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>Educate using “ask-tell-ask” rather than “tell-ask-tell”</t>
         </is>
       </c>
       <c r="P68" t="inlineStr"/>
@@ -2732,44 +2739,40 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>BCIO:044123</t>
+          <t>BCIO:050388</t>
         </is>
       </c>
       <c r="B69" t="inlineStr"/>
       <c r="C69" t="inlineStr"/>
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr"/>
-      <c r="F69" t="inlineStr"/>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>communication showing acknowledgement</t>
+        </is>
+      </c>
       <c r="G69" t="inlineStr"/>
       <c r="H69" t="inlineStr"/>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>warm communication style</t>
-        </is>
-      </c>
+      <c r="I69" t="inlineStr"/>
       <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr">
         <is>
-          <t>A communication style which demonstrates human interest and caring.</t>
-        </is>
-      </c>
-      <c r="N69" t="inlineStr">
-        <is>
-          <t>friendly communication style</t>
-        </is>
-      </c>
-      <c r="O69" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
+          <t>A communication involving the expressed recognition of what another has expressed.</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr"/>
       <c r="Q69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>BCIO:044097</t>
+          <t>BCIO:044021</t>
         </is>
       </c>
       <c r="B70" t="inlineStr"/>
@@ -2777,126 +2780,139 @@
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr"/>
-      <c r="G70" t="inlineStr"/>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>communication acknowledging difficulties</t>
+        </is>
+      </c>
       <c r="H70" t="inlineStr"/>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>conversational communication style</t>
-        </is>
-      </c>
+      <c r="I70" t="inlineStr"/>
       <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr">
         <is>
-          <t>A communication style that is typical of interpersonal dialogue which encourages an interactive exchange of ideas and beliefs.</t>
+          <t>A communication showing acknolwedgement conveying empathy or compassion towards a sub-optimal situation or concerns of a recipient.</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
         </is>
       </c>
       <c r="N70" t="inlineStr"/>
-      <c r="O70" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
       <c r="P70" t="inlineStr"/>
       <c r="Q70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>BCIO:044090</t>
+          <t>BCIO:044042</t>
         </is>
       </c>
       <c r="B71" t="inlineStr"/>
       <c r="C71" t="inlineStr"/>
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr"/>
-      <c r="F71" t="inlineStr"/>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>communication understating intensity of person's views</t>
+        </is>
+      </c>
       <c r="G71" t="inlineStr"/>
       <c r="H71" t="inlineStr"/>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>communication style conveying genuineness</t>
-        </is>
-      </c>
+      <c r="I71" t="inlineStr"/>
       <c r="J71" t="inlineStr"/>
       <c r="K71" t="inlineStr">
         <is>
-          <t>A communication style which suggests one is acting in line with one's true values and beliefs.</t>
-        </is>
-      </c>
-      <c r="N71" t="inlineStr">
-        <is>
-          <t>sincerity</t>
-        </is>
-      </c>
-      <c r="O71" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="P71" t="inlineStr"/>
+          <t>A communication using statements that diminish or understate the intensity of the content or emotion expressed by the other person.</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>"undershooting" in motivational interviewing</t>
+        </is>
+      </c>
       <c r="Q71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>BCIO:044081</t>
+          <t>BCIO:044018</t>
         </is>
       </c>
       <c r="B72" t="inlineStr"/>
       <c r="C72" t="inlineStr"/>
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr"/>
-      <c r="F72" t="inlineStr"/>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>branded communication</t>
+        </is>
+      </c>
       <c r="G72" t="inlineStr"/>
       <c r="H72" t="inlineStr"/>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>aloof communication style</t>
-        </is>
-      </c>
+      <c r="I72" t="inlineStr"/>
       <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr">
         <is>
-          <t>A communication style characterised by a lack of empathy or compassion for the recipient.</t>
-        </is>
-      </c>
-      <c r="N72" t="inlineStr"/>
-      <c r="O72" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="P72" t="inlineStr"/>
+          <t>A communication using a consistent style of text or graphics to identify and distinguish a product, service or intervention from other products, services or interventions.</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>Change for Life, Time to Change, NHS Smokefree</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>use of branding; brand identity</t>
+        </is>
+      </c>
       <c r="Q72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>BCIO:044096</t>
+          <t>BCIO:044019</t>
         </is>
       </c>
       <c r="B73" t="inlineStr"/>
       <c r="C73" t="inlineStr"/>
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr"/>
-      <c r="F73" t="inlineStr"/>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>discussion</t>
+        </is>
+      </c>
       <c r="G73" t="inlineStr"/>
       <c r="H73" t="inlineStr"/>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>controlling communication style</t>
-        </is>
-      </c>
+      <c r="I73" t="inlineStr"/>
       <c r="J73" t="inlineStr"/>
       <c r="K73" t="inlineStr">
         <is>
-          <t>A communication style which directly instructs the adoption of certain beliefs, theories or lines of action.</t>
+          <t>A communication involving an extended exchange of utterances between an instigator and at least one other person.</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
         </is>
       </c>
       <c r="N73" t="inlineStr"/>
       <c r="O73" t="inlineStr">
         <is>
-          <t>style of delivery</t>
+          <t>An utterance is an uninterrupted stretch of speech or writing produced by an individual on a particular occasion. An utterance can range from a single word to a complete sentence.</t>
         </is>
       </c>
       <c r="P73" t="inlineStr"/>
@@ -2905,7 +2921,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>BCIO:044127</t>
+          <t>BCIO:044020</t>
         </is>
       </c>
       <c r="B74" t="inlineStr"/>
@@ -2913,238 +2929,276 @@
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr"/>
       <c r="F74" t="inlineStr"/>
-      <c r="G74" t="inlineStr"/>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>object visual style</t>
-        </is>
-      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>classroom-style discussion</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr"/>
       <c r="I74" t="inlineStr"/>
       <c r="J74" t="inlineStr"/>
       <c r="K74" t="inlineStr">
         <is>
-          <t>An attribute of an object used in a communication process, concerning how information sensed with the eyes is presented, which may include colours/fonts/images/spacing/sizing.</t>
+          <t>A discussion led by the initiator in a manner typical of a teacher or lecturer.</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
         </is>
       </c>
       <c r="N74" t="inlineStr"/>
-      <c r="O74" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
       <c r="P74" t="inlineStr"/>
-      <c r="Q74" t="inlineStr">
-        <is>
-          <t>colour scheme chosen for a website, style of images used for a booklet, brightly coloured reminder stickers</t>
-        </is>
-      </c>
+      <c r="Q74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>BCIO:044130</t>
+          <t>BCIO:044049</t>
         </is>
       </c>
       <c r="B75" t="inlineStr"/>
       <c r="C75" t="inlineStr"/>
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr"/>
-      <c r="F75" t="inlineStr"/>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>communication using interjections to signal attentiveness</t>
+        </is>
+      </c>
       <c r="G75" t="inlineStr"/>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>readability</t>
-        </is>
-      </c>
+      <c r="H75" t="inlineStr"/>
       <c r="I75" t="inlineStr"/>
       <c r="J75" t="inlineStr"/>
       <c r="K75" t="inlineStr">
         <is>
-          <t>An attribute of a text used in communication process, concerning the ease of understanding the wording or other qualitative aspects of the text that facilitate comprehension.</t>
-        </is>
-      </c>
-      <c r="N75" t="inlineStr"/>
+          <t>A communication in which one person uses brief interjections to signal that they are listening to what the other person is saying.</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>Words like "interesting", "yeah"," mmhmm"</t>
+        </is>
+      </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="P75" t="inlineStr"/>
-      <c r="Q75" t="inlineStr">
-        <is>
-          <t>including adequate blank space and empty circles for the young people and their carers to record and review agenda items</t>
-        </is>
-      </c>
+          <t>An interjection is a word, phrase or exclamation which is typically unconnected to a sentence and is used to express an emotion or reaction.</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>"Back-channels" or "undertalk" in the Roter Interaction Analysis System</t>
+        </is>
+      </c>
+      <c r="Q75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>BCIO:044126</t>
+          <t>BCIO:044064</t>
         </is>
       </c>
       <c r="B76" t="inlineStr"/>
       <c r="C76" t="inlineStr"/>
       <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr"/>
-      <c r="F76" t="inlineStr"/>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>narrative communication</t>
+        </is>
+      </c>
       <c r="G76" t="inlineStr"/>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>oral communication pace</t>
-        </is>
-      </c>
+      <c r="H76" t="inlineStr"/>
       <c r="I76" t="inlineStr"/>
       <c r="J76" t="inlineStr"/>
       <c r="K76" t="inlineStr">
         <is>
-          <t>An attribute of an oral communication relating to the speed with which an individual speaks.</t>
+          <t>A communication describing the particulars of a person's life or a course of events in the style of telling a story.</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
         </is>
       </c>
       <c r="N76" t="inlineStr"/>
-      <c r="O76" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
       <c r="P76" t="inlineStr"/>
       <c r="Q76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>OGMS:0000060</t>
+          <t>BCIO:044037</t>
         </is>
       </c>
       <c r="B77" t="inlineStr"/>
       <c r="C77" t="inlineStr"/>
       <c r="D77" t="inlineStr"/>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>bodily process</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr"/>
+      <c r="E77" t="inlineStr"/>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>communication involving agreement</t>
+        </is>
+      </c>
       <c r="G77" t="inlineStr"/>
       <c r="H77" t="inlineStr"/>
       <c r="I77" t="inlineStr"/>
       <c r="J77" t="inlineStr"/>
       <c r="K77" t="inlineStr">
         <is>
-          <t>A process in which at least one bodily component of an organsim participates.</t>
-        </is>
-      </c>
+          <t>A communication in which one participant concurs with the views stated by another.</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr"/>
+      <c r="P77" t="inlineStr"/>
+      <c r="Q77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>BCIO:036000</t>
+          <t>BCIO:044038</t>
         </is>
       </c>
       <c r="B78" t="inlineStr"/>
       <c r="C78" t="inlineStr"/>
       <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr"/>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>individual human behaviour</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr"/>
+      <c r="F78" t="inlineStr"/>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>communication involving agreement followed by highlighting incongruent aspects</t>
+        </is>
+      </c>
       <c r="H78" t="inlineStr"/>
       <c r="I78" t="inlineStr"/>
       <c r="J78" t="inlineStr"/>
       <c r="K78" t="inlineStr">
         <is>
-          <t>A bodily process of a human that involves co-ordinated contraction of striated muscles controlled by the brain.</t>
-        </is>
-      </c>
+          <t>A communication involving agreement in which one participant concurs with the views stated by another and then points out an incongruent aspect of the situation under discussion.</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>"agreement with a twist" in motivational interviewing</t>
+        </is>
+      </c>
+      <c r="Q78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>BCIO:050441</t>
+          <t>BCIO:044078</t>
         </is>
       </c>
       <c r="B79" t="inlineStr"/>
       <c r="C79" t="inlineStr"/>
       <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr"/>
-      <c r="F79" t="inlineStr"/>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>socially-related behaviour</t>
-        </is>
-      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>shifting focus of communication</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr"/>
       <c r="H79" t="inlineStr"/>
       <c r="I79" t="inlineStr"/>
       <c r="J79" t="inlineStr"/>
       <c r="K79" t="inlineStr">
         <is>
-          <t>An individual human behaviour that relates to the social environment.</t>
-        </is>
-      </c>
+          <t>A communication that involves altering the area of greatest attention during the delivery of information.</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr"/>
+      <c r="P79" t="inlineStr"/>
+      <c r="Q79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>BCIO:036025</t>
+          <t>BCIO:044059</t>
         </is>
       </c>
       <c r="B80" t="inlineStr"/>
       <c r="C80" t="inlineStr"/>
       <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr"/>
-      <c r="F80" t="inlineStr"/>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>emotionally expressive communication</t>
+        </is>
+      </c>
       <c r="G80" t="inlineStr"/>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>inter-personal behaviour</t>
-        </is>
-      </c>
+      <c r="H80" t="inlineStr"/>
       <c r="I80" t="inlineStr"/>
       <c r="J80" t="inlineStr"/>
       <c r="K80" t="inlineStr">
         <is>
-          <t>An &lt;socially-related behaviour&gt; that involves an interaction between two or more people.</t>
+          <t>A communication in a manner which clearly conveys the emotions of the initiator.</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
         </is>
       </c>
       <c r="N80" t="inlineStr"/>
-      <c r="O80" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
       <c r="P80" t="inlineStr"/>
       <c r="Q80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>BCIO:036034</t>
+          <t>BCIO:044034</t>
         </is>
       </c>
       <c r="B81" t="inlineStr"/>
       <c r="C81" t="inlineStr"/>
       <c r="D81" t="inlineStr"/>
       <c r="E81" t="inlineStr"/>
-      <c r="F81" t="inlineStr"/>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>communication highlighting a contradiction</t>
+        </is>
+      </c>
       <c r="G81" t="inlineStr"/>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>human communication behaviour</t>
-        </is>
-      </c>
+      <c r="H81" t="inlineStr"/>
       <c r="I81" t="inlineStr"/>
       <c r="J81" t="inlineStr"/>
       <c r="K81" t="inlineStr">
         <is>
-          <t>An expressive behaviour that involves the transmission of information between two or more people.</t>
+          <t>A communication pointing out a situation in which actions or propositions are inconsistent with each other.</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
         </is>
       </c>
       <c r="N81" t="inlineStr"/>
       <c r="O81" t="inlineStr">
         <is>
-          <t>style of delivery</t>
+          <t>The contradiction can be between two or more of a person's actions, or between a person's actions and beliefs, or between two or more beliefs a person holds</t>
         </is>
       </c>
       <c r="P81" t="inlineStr"/>
@@ -3153,64 +3207,69 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>BCIO:050237</t>
+          <t>BCIO:044061</t>
         </is>
       </c>
       <c r="B82" t="inlineStr"/>
       <c r="C82" t="inlineStr"/>
       <c r="D82" t="inlineStr"/>
       <c r="E82" t="inlineStr"/>
-      <c r="F82" t="inlineStr"/>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>interrupting</t>
+        </is>
+      </c>
       <c r="G82" t="inlineStr"/>
       <c r="H82" t="inlineStr"/>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>linguistic communication behaviour</t>
-        </is>
-      </c>
+      <c r="I82" t="inlineStr"/>
       <c r="J82" t="inlineStr"/>
       <c r="K82" t="inlineStr">
         <is>
-          <t>A human communication behaviour in which the information that is communicated is encoded in language.</t>
+          <t>A communication in which one person interjects before another has finished making their point.</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
         </is>
       </c>
       <c r="N82" t="inlineStr"/>
-      <c r="O82" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
       <c r="P82" t="inlineStr"/>
       <c r="Q82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>BCIO:050457</t>
+          <t>BCIO:044001</t>
         </is>
       </c>
       <c r="B83" t="inlineStr"/>
       <c r="C83" t="inlineStr"/>
       <c r="D83" t="inlineStr"/>
       <c r="E83" t="inlineStr"/>
-      <c r="F83" t="inlineStr"/>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>expressive behaviour</t>
-        </is>
-      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>intervention content communication process</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr"/>
       <c r="H83" t="inlineStr"/>
       <c r="I83" t="inlineStr"/>
       <c r="J83" t="inlineStr"/>
       <c r="K83" t="inlineStr">
         <is>
-          <t>An individual human behaviour that conveys a thought or feeling.</t>
+          <t>A communication that transmits the content of an intervention</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
         </is>
       </c>
       <c r="N83" t="inlineStr"/>
       <c r="O83" t="inlineStr">
         <is>
-          <t>style of delivery</t>
+          <t>Note that an intervention is a planned process with the aim of influencing some outcome whereas a behaviour change intervention is an intervention that aims to influence human behaviour as an outcome.</t>
         </is>
       </c>
       <c r="P83" t="inlineStr"/>
@@ -3219,7 +3278,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>BCIO:050374</t>
+          <t>BCIO:044002</t>
         </is>
       </c>
       <c r="B84" t="inlineStr"/>
@@ -3227,23 +3286,28 @@
       <c r="D84" t="inlineStr"/>
       <c r="E84" t="inlineStr"/>
       <c r="F84" t="inlineStr"/>
-      <c r="G84" t="inlineStr"/>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>laughing</t>
-        </is>
-      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>behaviour change intervention content communication process</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr"/>
       <c r="I84" t="inlineStr"/>
       <c r="J84" t="inlineStr"/>
       <c r="K84" t="inlineStr">
         <is>
-          <t>An expressive behaviour showing elation, amusement or scorn by means of facial expressions and repeated sharp exhalations.</t>
+          <t>An intervention content communication process that is about behaviour change intervention content</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
         </is>
       </c>
       <c r="N84" t="inlineStr"/>
       <c r="O84" t="inlineStr">
         <is>
-          <t>style of delivery</t>
+          <t>A behaviour change intervention is a planned process that aims to influence human behaviour.  In contrast, an intervention is a planned process with the aim of influencing some outcome.  This outcome may be other than human behaviour.</t>
         </is>
       </c>
       <c r="P84" t="inlineStr"/>
@@ -3252,31 +3316,40 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>BCIO:050552</t>
+          <t>BCIO:044069</t>
         </is>
       </c>
       <c r="B85" t="inlineStr"/>
       <c r="C85" t="inlineStr"/>
       <c r="D85" t="inlineStr"/>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>communication channel</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr"/>
+      <c r="E85" t="inlineStr"/>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>offering reassurance</t>
+        </is>
+      </c>
       <c r="G85" t="inlineStr"/>
       <c r="H85" t="inlineStr"/>
       <c r="I85" t="inlineStr"/>
       <c r="J85" t="inlineStr"/>
       <c r="K85" t="inlineStr">
         <is>
-          <t>A &lt;process&gt; by which a communication is delivered.</t>
-        </is>
-      </c>
-      <c r="N85" t="inlineStr"/>
+          <t>A communication intended to provide hope and strength in times of anxiety, worry, confusion, grief, distress, or suffering.</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>made reassuring statements</t>
+        </is>
+      </c>
       <c r="O85" t="inlineStr">
         <is>
-          <t>style of delivery</t>
+          <t>based on Roter Interactional Analysis System</t>
         </is>
       </c>
       <c r="P85" t="inlineStr"/>
@@ -3285,36 +3358,36 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>BCIO:050384</t>
+          <t>BCIO:044017</t>
         </is>
       </c>
       <c r="B86" t="inlineStr"/>
       <c r="C86" t="inlineStr"/>
       <c r="D86" t="inlineStr"/>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>communication</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr"/>
+      <c r="E86" t="inlineStr"/>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>banter</t>
+        </is>
+      </c>
       <c r="G86" t="inlineStr"/>
       <c r="H86" t="inlineStr"/>
       <c r="I86" t="inlineStr"/>
       <c r="J86" t="inlineStr"/>
       <c r="K86" t="inlineStr">
         <is>
-          <t>A process involving the transmission of information between two or more participants.</t>
+          <t>A communication involving the exchange of light and teasing remarks intended to be playful.</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>The participants in the communication process can be of a variety of types, e.g. a human talking to an automated chatbot system, two computer systems exchanging information, a person talking to a pet animal etc.</t>
+          <t>style of delivery</t>
         </is>
       </c>
       <c r="N86" t="inlineStr"/>
       <c r="O86" t="inlineStr">
         <is>
-          <t>style of delivery</t>
+          <t>Note that teasing is an essential part of the definition of banter. For amusing or enjoyable communication, but without the element of teasing, using entertaining or humourous communication style. Also, note that banter may not always be perceived as playful by the subject of the remarks</t>
         </is>
       </c>
       <c r="P86" t="inlineStr"/>
@@ -3323,7 +3396,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>BCIO:044030</t>
+          <t>BCIO:044009</t>
         </is>
       </c>
       <c r="B87" t="inlineStr"/>
@@ -3332,7 +3405,7 @@
       <c r="E87" t="inlineStr"/>
       <c r="F87" t="inlineStr">
         <is>
-          <t>exploring communication</t>
+          <t>active listening</t>
         </is>
       </c>
       <c r="G87" t="inlineStr"/>
@@ -3341,106 +3414,72 @@
       <c r="J87" t="inlineStr"/>
       <c r="K87" t="inlineStr">
         <is>
-          <t>A communication to better understand what a person thinks or feels about a topic or an experience.</t>
+          <t>A communication involving one participant paying close attention to what is said by another, asking questions and reflecting as needed, in an attempt to fully understand what has been said.</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>This can include asking questions or prompting elaboration e.g 'Tell me more about that'</t>
+          <t>style of delivery</t>
         </is>
       </c>
       <c r="N87" t="inlineStr"/>
-      <c r="O87" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
       <c r="P87" t="inlineStr"/>
-      <c r="Q87" t="inlineStr">
-        <is>
-          <t>eliciting or seeking information</t>
-        </is>
-      </c>
+      <c r="Q87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>BCIO:050386</t>
+          <t>BFO:0000144</t>
         </is>
       </c>
       <c r="B88" t="inlineStr"/>
       <c r="C88" t="inlineStr"/>
       <c r="D88" t="inlineStr"/>
-      <c r="E88" t="inlineStr"/>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>process profile</t>
+        </is>
+      </c>
       <c r="F88" t="inlineStr"/>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>communication exploring a person's thoughts about a topic</t>
-        </is>
-      </c>
+      <c r="G88" t="inlineStr"/>
       <c r="H88" t="inlineStr"/>
       <c r="I88" t="inlineStr"/>
       <c r="J88" t="inlineStr"/>
       <c r="K88" t="inlineStr">
         <is>
-          <t>An exploring communication focused on what a person thinks about a matter.</t>
-        </is>
-      </c>
-      <c r="N88" t="inlineStr"/>
-      <c r="O88" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="P88" t="inlineStr"/>
-      <c r="Q88" t="inlineStr">
-        <is>
-          <t>clarifying what someone has said</t>
+          <t>b is a process_profile =Def. there is some process c such that b process_profile_of c (axiom label in BFO2 Reference: [093-002])</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>BCIO:050385</t>
+          <t>BCIO:043000</t>
         </is>
       </c>
       <c r="B89" t="inlineStr"/>
       <c r="C89" t="inlineStr"/>
       <c r="D89" t="inlineStr"/>
       <c r="E89" t="inlineStr"/>
-      <c r="F89" t="inlineStr"/>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>communication exploring a person's feelings about an experience</t>
-        </is>
-      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>process attribute</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr"/>
       <c r="H89" t="inlineStr"/>
       <c r="I89" t="inlineStr"/>
       <c r="J89" t="inlineStr"/>
       <c r="K89" t="inlineStr">
         <is>
-          <t>An exploring communication focused on a person's affective responses to an experience.</t>
-        </is>
-      </c>
-      <c r="L89" t="inlineStr">
-        <is>
-          <t>An experience can be any situation or state a person encounters or undergoes</t>
-        </is>
-      </c>
-      <c r="N89" t="inlineStr"/>
-      <c r="O89" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="P89" t="inlineStr"/>
-      <c r="Q89" t="inlineStr"/>
+          <t>A process profile that is an attribute of a process.</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>BCIO:050383</t>
+          <t>BCIO:044003</t>
         </is>
       </c>
       <c r="B90" t="inlineStr"/>
@@ -3450,7 +3489,7 @@
       <c r="F90" t="inlineStr"/>
       <c r="G90" t="inlineStr">
         <is>
-          <t>communication exploring a person's feelings about a topic</t>
+          <t>communication process attribute</t>
         </is>
       </c>
       <c r="H90" t="inlineStr"/>
@@ -3458,26 +3497,27 @@
       <c r="J90" t="inlineStr"/>
       <c r="K90" t="inlineStr">
         <is>
-          <t>An exploring communication focused on a person's affective responses to a matter.</t>
+          <t>An attribute of a communication process.</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
         </is>
       </c>
       <c r="N90" t="inlineStr"/>
       <c r="O90" t="inlineStr">
         <is>
-          <t>style of delivery</t>
+          <t>Communication processes can have a variety of attributes, such as their speed, how they are delivered, what language they take place in and the tone of voice in which they occur.  All these types of attributes and more are captured by "communication process attribute"</t>
         </is>
       </c>
       <c r="P90" t="inlineStr"/>
-      <c r="Q90" t="inlineStr">
-        <is>
-          <t>Elicit concerns, problems and reactions</t>
-        </is>
-      </c>
+      <c r="Q90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>BCIO:050387</t>
+          <t>BCIO:044129</t>
         </is>
       </c>
       <c r="B91" t="inlineStr"/>
@@ -3485,28 +3525,32 @@
       <c r="D91" t="inlineStr"/>
       <c r="E91" t="inlineStr"/>
       <c r="F91" t="inlineStr"/>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>communication exploring a person's thoughts about an experience</t>
-        </is>
-      </c>
-      <c r="H91" t="inlineStr"/>
+      <c r="G91" t="inlineStr"/>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>object layout</t>
+        </is>
+      </c>
       <c r="I91" t="inlineStr"/>
       <c r="J91" t="inlineStr"/>
       <c r="K91" t="inlineStr">
         <is>
-          <t>An exploring communication focused on what a person thinks about an experience.</t>
+          <t>An attribute of an object used in communication process, concerning how the object's components are arranged.</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>An experience can be any situation or state a person encounters or undergoes</t>
-        </is>
-      </c>
-      <c r="N91" t="inlineStr"/>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>arrangement of chairs in the room for a group intervention, amount of space between blocks of text in a leaflet, arrangement of sections of a website</t>
+        </is>
+      </c>
       <c r="O91" t="inlineStr">
         <is>
-          <t>style of delivery</t>
+          <t>the arrangement of components can be deliberately chosen to help communicate intervention content</t>
         </is>
       </c>
       <c r="P91" t="inlineStr"/>
@@ -3515,35 +3559,40 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>BCIO:044011</t>
+          <t>BCIO:044128</t>
         </is>
       </c>
       <c r="B92" t="inlineStr"/>
       <c r="C92" t="inlineStr"/>
       <c r="D92" t="inlineStr"/>
       <c r="E92" t="inlineStr"/>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>agenda-sharing communication</t>
-        </is>
-      </c>
+      <c r="F92" t="inlineStr"/>
       <c r="G92" t="inlineStr"/>
-      <c r="H92" t="inlineStr"/>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>source visual style</t>
+        </is>
+      </c>
       <c r="I92" t="inlineStr"/>
       <c r="J92" t="inlineStr"/>
       <c r="K92" t="inlineStr">
         <is>
-          <t>A communication in which the initiator and one or more activity participants work together to determine a focus for the activity to be undertaken.</t>
+          <t>An attribute of an intervention person source concerning how they appear to others.</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
         </is>
       </c>
       <c r="N92" t="inlineStr">
         <is>
-          <t>agenda mapping</t>
+          <t>Health care professionals' uniform to convey authority and knowledge, doctors not wearing white coats to speak to children</t>
         </is>
       </c>
       <c r="O92" t="inlineStr">
         <is>
-          <t>style of delivery</t>
+          <t>may be purposefully chosen to convey certain attributes of the source</t>
         </is>
       </c>
       <c r="P92" t="inlineStr"/>
@@ -3552,105 +3601,110 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>BCIO:044039</t>
+          <t>BCIO:044004</t>
         </is>
       </c>
       <c r="B93" t="inlineStr"/>
       <c r="C93" t="inlineStr"/>
       <c r="D93" t="inlineStr"/>
       <c r="E93" t="inlineStr"/>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>communication involving confirmatory rephrasing</t>
-        </is>
-      </c>
+      <c r="F93" t="inlineStr"/>
       <c r="G93" t="inlineStr"/>
-      <c r="H93" t="inlineStr"/>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>communication style</t>
+        </is>
+      </c>
       <c r="I93" t="inlineStr"/>
       <c r="J93" t="inlineStr"/>
       <c r="K93" t="inlineStr">
         <is>
-          <t>A communication involving the initiator rephrasing what a recipient says in a manner intended to confirm understanding of the recipient's situation rather than confront.</t>
-        </is>
-      </c>
-      <c r="N93" t="inlineStr">
-        <is>
-          <t>"coming alongside" in Motivational Interviewing</t>
-        </is>
-      </c>
-      <c r="O93" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
+          <t>A particular manner of communicating aimed at inducing or avoiding certain kinds of responses in others, or demonstrating certain characteristics of the initiator.</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr"/>
       <c r="Q93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>BCIO:044027</t>
+          <t>BCIO:044084</t>
         </is>
       </c>
       <c r="B94" t="inlineStr"/>
       <c r="C94" t="inlineStr"/>
       <c r="D94" t="inlineStr"/>
       <c r="E94" t="inlineStr"/>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>communication checking for own understanding</t>
-        </is>
-      </c>
+      <c r="F94" t="inlineStr"/>
       <c r="G94" t="inlineStr"/>
       <c r="H94" t="inlineStr"/>
-      <c r="I94" t="inlineStr"/>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>autonomy-supportive communication style</t>
+        </is>
+      </c>
       <c r="J94" t="inlineStr"/>
       <c r="K94" t="inlineStr">
         <is>
-          <t>A communication in which the instigator asks questions to determine if they have correctly comprehended the information presented by another.</t>
+          <t>A communication style which aims to promote the recipient's capacity to make their own decisions.</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
         </is>
       </c>
       <c r="N94" t="inlineStr"/>
       <c r="O94" t="inlineStr">
         <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="P94" t="inlineStr"/>
-      <c r="Q94" t="inlineStr">
-        <is>
-          <t>clarifying what another has said</t>
-        </is>
-      </c>
+          <t>from Self-Determination Theory interventions.</t>
+        </is>
+      </c>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>needs-supportive communication style</t>
+        </is>
+      </c>
+      <c r="Q94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>BCIO:044062</t>
+          <t>BCIO:044113</t>
         </is>
       </c>
       <c r="B95" t="inlineStr"/>
       <c r="C95" t="inlineStr"/>
       <c r="D95" t="inlineStr"/>
       <c r="E95" t="inlineStr"/>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>communication avoiding interrupting</t>
-        </is>
-      </c>
+      <c r="F95" t="inlineStr"/>
       <c r="G95" t="inlineStr"/>
       <c r="H95" t="inlineStr"/>
-      <c r="I95" t="inlineStr"/>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>patient communication style</t>
+        </is>
+      </c>
       <c r="J95" t="inlineStr"/>
       <c r="K95" t="inlineStr">
         <is>
-          <t>A communication in which at least one participant endeavours to not interject before another participant has finished making their point.</t>
-        </is>
-      </c>
-      <c r="N95" t="inlineStr"/>
-      <c r="O95" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
+          <t>A communication style conveying willingness to take time to understand or complete a process.</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>"willing to listen"</t>
         </is>
       </c>
       <c r="P95" t="inlineStr"/>
@@ -3659,64 +3713,69 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>BCIO:044065</t>
+          <t>BCIO:044122</t>
         </is>
       </c>
       <c r="B96" t="inlineStr"/>
       <c r="C96" t="inlineStr"/>
       <c r="D96" t="inlineStr"/>
       <c r="E96" t="inlineStr"/>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>negotiation</t>
-        </is>
-      </c>
+      <c r="F96" t="inlineStr"/>
       <c r="G96" t="inlineStr"/>
       <c r="H96" t="inlineStr"/>
-      <c r="I96" t="inlineStr"/>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>verbally dominant communication style</t>
+        </is>
+      </c>
       <c r="J96" t="inlineStr"/>
       <c r="K96" t="inlineStr">
         <is>
-          <t>A communication involving goal-oriented collaboration to arrive at an agreement or compromise on a matter of importance to the individuals involved.</t>
+          <t>A communication style characterised by one participant having more control over a conversation than the other.</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
         </is>
       </c>
       <c r="N96" t="inlineStr"/>
-      <c r="O96" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
       <c r="P96" t="inlineStr"/>
       <c r="Q96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>BCIO:044061</t>
+          <t>BCIO:044106</t>
         </is>
       </c>
       <c r="B97" t="inlineStr"/>
       <c r="C97" t="inlineStr"/>
       <c r="D97" t="inlineStr"/>
       <c r="E97" t="inlineStr"/>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>interrupting</t>
-        </is>
-      </c>
+      <c r="F97" t="inlineStr"/>
       <c r="G97" t="inlineStr"/>
       <c r="H97" t="inlineStr"/>
-      <c r="I97" t="inlineStr"/>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>informal communication style</t>
+        </is>
+      </c>
       <c r="J97" t="inlineStr"/>
       <c r="K97" t="inlineStr">
         <is>
-          <t>A communication in which one person interjects before another has finished making their point.</t>
+          <t>A communication style characterised by the use of casual or colloquial language rather than formal language.</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
         </is>
       </c>
       <c r="N97" t="inlineStr"/>
       <c r="O97" t="inlineStr">
         <is>
-          <t>style of delivery</t>
+          <t>"Colloquial" language is language that is typically used in ordinary conversation rather than in formal communication</t>
         </is>
       </c>
       <c r="P97" t="inlineStr"/>
@@ -3725,185 +3784,186 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>BCIO:044064</t>
+          <t>BCIO:044114</t>
         </is>
       </c>
       <c r="B98" t="inlineStr"/>
       <c r="C98" t="inlineStr"/>
       <c r="D98" t="inlineStr"/>
       <c r="E98" t="inlineStr"/>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>narrative communication</t>
-        </is>
-      </c>
+      <c r="F98" t="inlineStr"/>
       <c r="G98" t="inlineStr"/>
       <c r="H98" t="inlineStr"/>
-      <c r="I98" t="inlineStr"/>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>persuasive communication style</t>
+        </is>
+      </c>
       <c r="J98" t="inlineStr"/>
       <c r="K98" t="inlineStr">
         <is>
-          <t>A communication describing the particulars of a person's life or a course of events in the style of telling a story.</t>
+          <t>A communication style which aims to induce or urge the adoption of certain beliefs, theories or lines of action.</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
         </is>
       </c>
       <c r="N98" t="inlineStr"/>
-      <c r="O98" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
       <c r="P98" t="inlineStr"/>
       <c r="Q98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>BCIO:044023</t>
+          <t>BCIO:044100</t>
         </is>
       </c>
       <c r="B99" t="inlineStr"/>
       <c r="C99" t="inlineStr"/>
       <c r="D99" t="inlineStr"/>
       <c r="E99" t="inlineStr"/>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>communication asking permission to provide information and advice</t>
-        </is>
-      </c>
+      <c r="F99" t="inlineStr"/>
       <c r="G99" t="inlineStr"/>
       <c r="H99" t="inlineStr"/>
-      <c r="I99" t="inlineStr"/>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>easily comprehended communication style</t>
+        </is>
+      </c>
       <c r="J99" t="inlineStr"/>
       <c r="K99" t="inlineStr">
         <is>
-          <t>A communication which involves asking for approval before sharing knowledge and giving guidance.</t>
-        </is>
-      </c>
-      <c r="N99" t="inlineStr"/>
+          <t>A communication style characterised by using language in a manner intended to be easily understandable to a recipient.</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>using non-technical language, using clear language, avoiding jargon</t>
+        </is>
+      </c>
       <c r="O99" t="inlineStr">
         <is>
-          <t>style of delivery</t>
+          <t>This can involve using plain and simple language</t>
         </is>
       </c>
       <c r="P99" t="inlineStr"/>
-      <c r="Q99" t="inlineStr">
-        <is>
-          <t>Educate using “ask-tell-ask” rather than “tell-ask-tell”</t>
-        </is>
-      </c>
+      <c r="Q99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>BCIO:044022</t>
+          <t>BCIO:044109</t>
         </is>
       </c>
       <c r="B100" t="inlineStr"/>
       <c r="C100" t="inlineStr"/>
       <c r="D100" t="inlineStr"/>
       <c r="E100" t="inlineStr"/>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>communication adding intensity to another's views</t>
-        </is>
-      </c>
+      <c r="F100" t="inlineStr"/>
       <c r="G100" t="inlineStr"/>
       <c r="H100" t="inlineStr"/>
-      <c r="I100" t="inlineStr"/>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>legitimising communication style</t>
+        </is>
+      </c>
       <c r="J100" t="inlineStr"/>
       <c r="K100" t="inlineStr">
         <is>
-          <t>A communication using statements that add intensity to the content or emotion expressed by another person.</t>
-        </is>
-      </c>
-      <c r="N100" t="inlineStr">
-        <is>
-          <t>"overshooting" in motivational interviewing</t>
-        </is>
-      </c>
+          <t>A communication style characterised by making a person feel that their perspective or emotions are legitimate.</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr"/>
       <c r="O100" t="inlineStr">
         <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="P100" t="inlineStr"/>
+          <t>This entails a deliberate strategy to make the person feel their perspective is legitimate</t>
+        </is>
+      </c>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>validating emotions</t>
+        </is>
+      </c>
       <c r="Q100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>BCIO:044048</t>
+          <t>BCIO:044096</t>
         </is>
       </c>
       <c r="B101" t="inlineStr"/>
       <c r="C101" t="inlineStr"/>
       <c r="D101" t="inlineStr"/>
       <c r="E101" t="inlineStr"/>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>communication using deliberate pauses</t>
-        </is>
-      </c>
+      <c r="F101" t="inlineStr"/>
       <c r="G101" t="inlineStr"/>
       <c r="H101" t="inlineStr"/>
-      <c r="I101" t="inlineStr"/>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>controlling communication style</t>
+        </is>
+      </c>
       <c r="J101" t="inlineStr"/>
       <c r="K101" t="inlineStr">
         <is>
-          <t>A communication in which the speaker purposely leaves gaps between or after their speech utterances.</t>
+          <t>A communication style which directly instructs the adoption of certain beliefs, theories or lines of action.</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>Pauses may be deliberately left to provide opportunities for others to speak or reflect, or to demonstrate non-directiveness.</t>
+          <t>style of delivery</t>
         </is>
       </c>
       <c r="N101" t="inlineStr"/>
-      <c r="O101" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
       <c r="P101" t="inlineStr"/>
-      <c r="Q101" t="inlineStr">
-        <is>
-          <t>staying silent (where this is intended to give others the chance to speak)</t>
-        </is>
-      </c>
+      <c r="Q101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>BCIO:044034</t>
+          <t>BCIO:044005</t>
         </is>
       </c>
       <c r="B102" t="inlineStr"/>
       <c r="C102" t="inlineStr"/>
       <c r="D102" t="inlineStr"/>
       <c r="E102" t="inlineStr"/>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>communication highlighting a contradiction</t>
-        </is>
-      </c>
+      <c r="F102" t="inlineStr"/>
       <c r="G102" t="inlineStr"/>
       <c r="H102" t="inlineStr"/>
-      <c r="I102" t="inlineStr"/>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>intervention style of delivery</t>
+        </is>
+      </c>
       <c r="J102" t="inlineStr"/>
       <c r="K102" t="inlineStr">
         <is>
-          <t>A communication pointing out a situation in which actions or propositions are inconsistent with each other.</t>
+          <t>A communication style that is an attribute of an intervention content communication process.</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>The contradiction can be between two or more of a person's actions, or between a person's actions and beliefs, or between two or more beliefs a person holds</t>
+          <t>style of delivery</t>
         </is>
       </c>
       <c r="N102" t="inlineStr"/>
       <c r="O102" t="inlineStr">
         <is>
-          <t>style of delivery</t>
+          <t>when a communication style is used as part of an intervention content communication process, then it qualifies as an intervention style of delivery</t>
         </is>
       </c>
       <c r="P102" t="inlineStr"/>
@@ -3912,429 +3972,423 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>BCIO:044035</t>
+          <t>BCIO:044123</t>
         </is>
       </c>
       <c r="B103" t="inlineStr"/>
       <c r="C103" t="inlineStr"/>
       <c r="D103" t="inlineStr"/>
       <c r="E103" t="inlineStr"/>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>communication inviting reactions to content presented</t>
-        </is>
-      </c>
+      <c r="F103" t="inlineStr"/>
       <c r="G103" t="inlineStr"/>
       <c r="H103" t="inlineStr"/>
-      <c r="I103" t="inlineStr"/>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>warm communication style</t>
+        </is>
+      </c>
       <c r="J103" t="inlineStr"/>
       <c r="K103" t="inlineStr">
         <is>
-          <t>A communication seeking information about a person's responses to the  content presented.</t>
-        </is>
-      </c>
-      <c r="N103" t="inlineStr">
-        <is>
-          <t>asking for opinions</t>
-        </is>
-      </c>
-      <c r="O103" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="P103" t="inlineStr"/>
+          <t>A communication style which demonstrates human interest and caring.</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="N103" t="inlineStr"/>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>friendly communication style</t>
+        </is>
+      </c>
       <c r="Q103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>BCIO:044059</t>
+          <t>BCIO:050390</t>
         </is>
       </c>
       <c r="B104" t="inlineStr"/>
       <c r="C104" t="inlineStr"/>
       <c r="D104" t="inlineStr"/>
       <c r="E104" t="inlineStr"/>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>emotionally expressive communication</t>
-        </is>
-      </c>
+      <c r="F104" t="inlineStr"/>
       <c r="G104" t="inlineStr"/>
       <c r="H104" t="inlineStr"/>
-      <c r="I104" t="inlineStr"/>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>humorous communication style</t>
+        </is>
+      </c>
       <c r="J104" t="inlineStr"/>
       <c r="K104" t="inlineStr">
         <is>
-          <t>A communication in a manner which clearly conveys the emotions of the initiator.</t>
+          <t>A communication style intended to amuse.</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
         </is>
       </c>
       <c r="N104" t="inlineStr"/>
-      <c r="O104" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
       <c r="P104" t="inlineStr"/>
       <c r="Q104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>BCIO:044070</t>
+          <t>BCIO:044081</t>
         </is>
       </c>
       <c r="B105" t="inlineStr"/>
       <c r="C105" t="inlineStr"/>
       <c r="D105" t="inlineStr"/>
       <c r="E105" t="inlineStr"/>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>paraphrasing</t>
-        </is>
-      </c>
+      <c r="F105" t="inlineStr"/>
       <c r="G105" t="inlineStr"/>
       <c r="H105" t="inlineStr"/>
-      <c r="I105" t="inlineStr"/>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>aloof communication style</t>
+        </is>
+      </c>
       <c r="J105" t="inlineStr"/>
       <c r="K105" t="inlineStr">
         <is>
-          <t>A communication in which one participant summarises what the other said.</t>
+          <t>A communication style characterised by a lack of empathy or compassion for the recipient.</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>This class is different to "communication involving confirmatory rephrasing" as this class is simply about summarising what another person said.</t>
+          <t>style of delivery</t>
         </is>
       </c>
       <c r="N105" t="inlineStr"/>
-      <c r="O105" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
       <c r="P105" t="inlineStr"/>
       <c r="Q105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>BCIO:044058</t>
+          <t>BCIO:044104</t>
         </is>
       </c>
       <c r="B106" t="inlineStr"/>
       <c r="C106" t="inlineStr"/>
       <c r="D106" t="inlineStr"/>
       <c r="E106" t="inlineStr"/>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>communication using rational arguments</t>
-        </is>
-      </c>
+      <c r="F106" t="inlineStr"/>
       <c r="G106" t="inlineStr"/>
       <c r="H106" t="inlineStr"/>
-      <c r="I106" t="inlineStr"/>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>formal communication style</t>
+        </is>
+      </c>
       <c r="J106" t="inlineStr"/>
       <c r="K106" t="inlineStr">
         <is>
-          <t>A communication that involves the use of declarative propositions based on what the communicator believes to be logical.</t>
+          <t>A communication style characterised by the use of traditional standards of correctness and etiquette and without casual, contracted, or colloquial forms of language.</t>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
         </is>
       </c>
       <c r="N106" t="inlineStr"/>
-      <c r="O106" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
       <c r="P106" t="inlineStr"/>
       <c r="Q106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>BCIO:044036</t>
+          <t>BCIO:044111</t>
         </is>
       </c>
       <c r="B107" t="inlineStr"/>
       <c r="C107" t="inlineStr"/>
       <c r="D107" t="inlineStr"/>
       <c r="E107" t="inlineStr"/>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>communication involving acceptance that recipients views may be different to the initiator's views</t>
-        </is>
-      </c>
+      <c r="F107" t="inlineStr"/>
       <c r="G107" t="inlineStr"/>
       <c r="H107" t="inlineStr"/>
-      <c r="I107" t="inlineStr"/>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>non-confrontational communication style</t>
+        </is>
+      </c>
       <c r="J107" t="inlineStr"/>
       <c r="K107" t="inlineStr">
         <is>
-          <t>A communication involving accepting that the recipient has different beliefs to the initiator and continuing with the planned activities while allowing both views to exist.</t>
+          <t>A communication style characterised by being diplomatic and avoiding conflict.</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>From Motivational Interviewing</t>
+          <t>style of delivery</t>
         </is>
       </c>
       <c r="N107" t="inlineStr"/>
-      <c r="O107" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
       <c r="P107" t="inlineStr"/>
       <c r="Q107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>BCIO:044042</t>
+          <t>BCIO:044107</t>
         </is>
       </c>
       <c r="B108" t="inlineStr"/>
       <c r="C108" t="inlineStr"/>
       <c r="D108" t="inlineStr"/>
       <c r="E108" t="inlineStr"/>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>communication understating intensity of person's views</t>
-        </is>
-      </c>
+      <c r="F108" t="inlineStr"/>
       <c r="G108" t="inlineStr"/>
       <c r="H108" t="inlineStr"/>
-      <c r="I108" t="inlineStr"/>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>intellectual communication style</t>
+        </is>
+      </c>
       <c r="J108" t="inlineStr"/>
       <c r="K108" t="inlineStr">
         <is>
-          <t>A communication using statements that diminish or understate the intensity of the content or emotion expressed by the other person.</t>
-        </is>
-      </c>
-      <c r="N108" t="inlineStr">
-        <is>
-          <t>"undershooting" in motivational interviewing</t>
-        </is>
-      </c>
-      <c r="O108" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
+          <t>A communication style characterised by an emphasis on reasoning and promoting objective understanding.</t>
+        </is>
+      </c>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="N108" t="inlineStr"/>
       <c r="P108" t="inlineStr"/>
       <c r="Q108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>BCIO:044010</t>
+          <t>BCIO:044119</t>
         </is>
       </c>
       <c r="B109" t="inlineStr"/>
       <c r="C109" t="inlineStr"/>
       <c r="D109" t="inlineStr"/>
       <c r="E109" t="inlineStr"/>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>affirming communication</t>
-        </is>
-      </c>
+      <c r="F109" t="inlineStr"/>
       <c r="G109" t="inlineStr"/>
       <c r="H109" t="inlineStr"/>
-      <c r="I109" t="inlineStr"/>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>semi-structured communication style</t>
+        </is>
+      </c>
       <c r="J109" t="inlineStr"/>
       <c r="K109" t="inlineStr">
         <is>
-          <t>A communication involving acknowledging another's strength or resilience in a given context or situation.</t>
-        </is>
-      </c>
-      <c r="N109" t="inlineStr"/>
-      <c r="O109" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="P109" t="inlineStr"/>
-      <c r="Q109" t="inlineStr">
-        <is>
-          <t>Making explicit statements of partnership or support; Shows approval;</t>
-        </is>
-      </c>
+          <t>A communication style involving the communication content having some constituent pre-planned parts but also being responsive to inputs.</t>
+        </is>
+      </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="N109" t="inlineStr">
+        <is>
+          <t>Using talking points, using conversation guides, having a list of topics to cover</t>
+        </is>
+      </c>
+      <c r="P109" t="inlineStr">
+        <is>
+          <t>organised communication style</t>
+        </is>
+      </c>
+      <c r="Q109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>BCIO:044040</t>
+          <t>BCIO:044116</t>
         </is>
       </c>
       <c r="B110" t="inlineStr"/>
       <c r="C110" t="inlineStr"/>
       <c r="D110" t="inlineStr"/>
       <c r="E110" t="inlineStr"/>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>communication involving elaboration of arguments</t>
-        </is>
-      </c>
+      <c r="F110" t="inlineStr"/>
       <c r="G110" t="inlineStr"/>
       <c r="H110" t="inlineStr"/>
-      <c r="I110" t="inlineStr"/>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>relaxed communication style</t>
+        </is>
+      </c>
       <c r="J110" t="inlineStr"/>
       <c r="K110" t="inlineStr">
         <is>
-          <t>A communication further developing a declarative statement that has been made  by making it clearer, more precise, bringing out its consequences or giving a concrete example.</t>
+          <t>A communication style characterised by a lack of tension or anxiety.</t>
+        </is>
+      </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
         </is>
       </c>
       <c r="N110" t="inlineStr"/>
-      <c r="O110" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="P110" t="inlineStr"/>
+      <c r="P110" t="inlineStr">
+        <is>
+          <t>calm communication style</t>
+        </is>
+      </c>
       <c r="Q110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>BCIO:044026</t>
+          <t>BCIO:044101</t>
         </is>
       </c>
       <c r="B111" t="inlineStr"/>
       <c r="C111" t="inlineStr"/>
       <c r="D111" t="inlineStr"/>
       <c r="E111" t="inlineStr"/>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>communication checking for others' understanding</t>
-        </is>
-      </c>
+      <c r="F111" t="inlineStr"/>
       <c r="G111" t="inlineStr"/>
       <c r="H111" t="inlineStr"/>
-      <c r="I111" t="inlineStr"/>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>empathic communication style</t>
+        </is>
+      </c>
       <c r="J111" t="inlineStr"/>
       <c r="K111" t="inlineStr">
         <is>
-          <t>A communication in which the instigator asks questions to determine if the recipient has comprehended information that has been presented.</t>
+          <t>A communication style which conveys an insightful awareness of the feelings and behaviours of the recipient.</t>
+        </is>
+      </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
         </is>
       </c>
       <c r="N111" t="inlineStr"/>
-      <c r="O111" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="P111" t="inlineStr"/>
+      <c r="P111" t="inlineStr">
+        <is>
+          <t>sensitivity, compassion</t>
+        </is>
+      </c>
       <c r="Q111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>BCIO:044018</t>
+          <t>BCIO:044112</t>
         </is>
       </c>
       <c r="B112" t="inlineStr"/>
       <c r="C112" t="inlineStr"/>
       <c r="D112" t="inlineStr"/>
       <c r="E112" t="inlineStr"/>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>branded communication</t>
-        </is>
-      </c>
+      <c r="F112" t="inlineStr"/>
       <c r="G112" t="inlineStr"/>
       <c r="H112" t="inlineStr"/>
-      <c r="I112" t="inlineStr"/>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>non-judgmental communication style</t>
+        </is>
+      </c>
       <c r="J112" t="inlineStr"/>
       <c r="K112" t="inlineStr">
         <is>
-          <t>A communication using a consistent style of text or graphics to identify and distinguish a product, service or intervention from other products, services or interventions.</t>
-        </is>
-      </c>
-      <c r="N112" t="inlineStr">
-        <is>
-          <t>use of branding; brand identity</t>
-        </is>
-      </c>
-      <c r="O112" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
+          <t>A communication style that demonstrates that one is not assigning a positive or negative valence to another's views or behaviours.</t>
+        </is>
+      </c>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="N112" t="inlineStr"/>
       <c r="P112" t="inlineStr"/>
-      <c r="Q112" t="inlineStr">
-        <is>
-          <t>Change for Life, Time to Change, NHS Smokefree</t>
-        </is>
-      </c>
+      <c r="Q112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>BCIO:044077</t>
+          <t>BCIO:044087</t>
         </is>
       </c>
       <c r="B113" t="inlineStr"/>
       <c r="C113" t="inlineStr"/>
       <c r="D113" t="inlineStr"/>
       <c r="E113" t="inlineStr"/>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>script-based communication</t>
-        </is>
-      </c>
+      <c r="F113" t="inlineStr"/>
       <c r="G113" t="inlineStr"/>
       <c r="H113" t="inlineStr"/>
-      <c r="I113" t="inlineStr"/>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>communication style conveying acceptance</t>
+        </is>
+      </c>
       <c r="J113" t="inlineStr"/>
       <c r="K113" t="inlineStr">
         <is>
-          <t>A communication which follows a pre-written sequence of instructions that are interpreted or carried out by a person or by a program.</t>
+          <t>A communication style that conveys respect and regard for the recipient as an individual.</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>This class involves tightly following a set of written instructions. It is different to structured communication style, which is a pre-planned style but not to the extent of using a written script.</t>
+          <t>style of delivery</t>
         </is>
       </c>
       <c r="N113" t="inlineStr"/>
-      <c r="O113" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
       <c r="P113" t="inlineStr"/>
       <c r="Q113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>BCIO:044041</t>
+          <t>BCIO:044099</t>
         </is>
       </c>
       <c r="B114" t="inlineStr"/>
       <c r="C114" t="inlineStr"/>
       <c r="D114" t="inlineStr"/>
       <c r="E114" t="inlineStr"/>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>communication offering choice</t>
-        </is>
-      </c>
+      <c r="F114" t="inlineStr"/>
       <c r="G114" t="inlineStr"/>
       <c r="H114" t="inlineStr"/>
-      <c r="I114" t="inlineStr"/>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>directive communication style</t>
+        </is>
+      </c>
       <c r="J114" t="inlineStr"/>
       <c r="K114" t="inlineStr">
         <is>
-          <t>A communication involving the initiator offering a range of options to the recipient.</t>
-        </is>
-      </c>
-      <c r="N114" t="inlineStr"/>
+          <t>A communication style intended to play an active role in another person's decision making.</t>
+        </is>
+      </c>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="N114" t="inlineStr">
+        <is>
+          <t>http://purl.bioontology.org/ontology/MESH/D037001</t>
+        </is>
+      </c>
       <c r="O114" t="inlineStr">
         <is>
-          <t>style of delivery</t>
+          <t>Note that this class is different from direct communication style</t>
         </is>
       </c>
       <c r="P114" t="inlineStr"/>
@@ -4343,45 +4397,44 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>BCIO:044043</t>
+          <t>BCIO:044103</t>
         </is>
       </c>
       <c r="B115" t="inlineStr"/>
       <c r="C115" t="inlineStr"/>
       <c r="D115" t="inlineStr"/>
       <c r="E115" t="inlineStr"/>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>communication using a particular form of address</t>
-        </is>
-      </c>
+      <c r="F115" t="inlineStr"/>
       <c r="G115" t="inlineStr"/>
       <c r="H115" t="inlineStr"/>
-      <c r="I115" t="inlineStr"/>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>entertaining communication style</t>
+        </is>
+      </c>
       <c r="J115" t="inlineStr"/>
       <c r="K115" t="inlineStr">
         <is>
-          <t>A communication addressing a person using a certain name or title to refer to that person.</t>
+          <t>A communication style intended to be amusing or enjoyable for the recipient.</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>The child classes of this class are specific types of address, whereas this class is for a non-specific type of address.</t>
+          <t>style of delivery</t>
         </is>
       </c>
       <c r="N115" t="inlineStr"/>
-      <c r="O115" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="P115" t="inlineStr"/>
+      <c r="P115" t="inlineStr">
+        <is>
+          <t>fun</t>
+        </is>
+      </c>
       <c r="Q115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>BCIO:044045</t>
+          <t>BCIO:050391</t>
         </is>
       </c>
       <c r="B116" t="inlineStr"/>
@@ -4389,32 +4442,32 @@
       <c r="D116" t="inlineStr"/>
       <c r="E116" t="inlineStr"/>
       <c r="F116" t="inlineStr"/>
-      <c r="G116" t="inlineStr">
-        <is>
-          <t>communication using informal address</t>
-        </is>
-      </c>
+      <c r="G116" t="inlineStr"/>
       <c r="H116" t="inlineStr"/>
-      <c r="I116" t="inlineStr"/>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>non-responsive communication style</t>
+        </is>
+      </c>
       <c r="J116" t="inlineStr"/>
       <c r="K116" t="inlineStr">
         <is>
-          <t>A communication addressing a person using a casual or colloquial name or title to refer to that person.</t>
+          <t>A communication style characterised by not adapting to the views and behaviours of the recipient.</t>
+        </is>
+      </c>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
         </is>
       </c>
       <c r="N116" t="inlineStr"/>
-      <c r="O116" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
       <c r="P116" t="inlineStr"/>
       <c r="Q116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>BCIO:044044</t>
+          <t>BCIO:044089</t>
         </is>
       </c>
       <c r="B117" t="inlineStr"/>
@@ -4422,32 +4475,32 @@
       <c r="D117" t="inlineStr"/>
       <c r="E117" t="inlineStr"/>
       <c r="F117" t="inlineStr"/>
-      <c r="G117" t="inlineStr">
-        <is>
-          <t>communication using formal address</t>
-        </is>
-      </c>
+      <c r="G117" t="inlineStr"/>
       <c r="H117" t="inlineStr"/>
-      <c r="I117" t="inlineStr"/>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>communication style conveying concern</t>
+        </is>
+      </c>
       <c r="J117" t="inlineStr"/>
       <c r="K117" t="inlineStr">
         <is>
-          <t>A communication addressing a person using a formal, legal or official name or title to refer to that person.</t>
+          <t>A communication style demonstrating one perceives an unwanted circumstance for the recipient.</t>
+        </is>
+      </c>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
         </is>
       </c>
       <c r="N117" t="inlineStr"/>
-      <c r="O117" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
       <c r="P117" t="inlineStr"/>
       <c r="Q117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>BCIO:044046</t>
+          <t>BCIO:044118</t>
         </is>
       </c>
       <c r="B118" t="inlineStr"/>
@@ -4455,60 +4508,65 @@
       <c r="D118" t="inlineStr"/>
       <c r="E118" t="inlineStr"/>
       <c r="F118" t="inlineStr"/>
-      <c r="G118" t="inlineStr">
-        <is>
-          <t>communication using preferred form of address</t>
-        </is>
-      </c>
+      <c r="G118" t="inlineStr"/>
       <c r="H118" t="inlineStr"/>
-      <c r="I118" t="inlineStr"/>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>responsive communication style</t>
+        </is>
+      </c>
       <c r="J118" t="inlineStr"/>
       <c r="K118" t="inlineStr">
         <is>
-          <t>A communication addressing a person using a name or title that the person has specified the instigator should use.</t>
+          <t>A communication style characterised by adapting to the views and behaviours of the recipient.</t>
+        </is>
+      </c>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
         </is>
       </c>
       <c r="N118" t="inlineStr"/>
       <c r="O118" t="inlineStr">
         <is>
-          <t>style of delivery</t>
+          <t>This class is adapting response as a result of how another person is communicating. In contrast, respectful communication style involves showing regard for the feelings etc of others from the outset, but not necessarily adapting one's own communication based on what the other says</t>
         </is>
       </c>
       <c r="P118" t="inlineStr"/>
-      <c r="Q118" t="inlineStr">
-        <is>
-          <t>Depending on whether Suzie Jones prefers to be addressed formally, or by her given name, saying either "Hello Mrs Jones" or "Hello Suzie"</t>
-        </is>
-      </c>
+      <c r="Q118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>BCIO:044078</t>
+          <t>BCIO:044108</t>
         </is>
       </c>
       <c r="B119" t="inlineStr"/>
       <c r="C119" t="inlineStr"/>
       <c r="D119" t="inlineStr"/>
       <c r="E119" t="inlineStr"/>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>shifting focus of communication</t>
-        </is>
-      </c>
+      <c r="F119" t="inlineStr"/>
       <c r="G119" t="inlineStr"/>
       <c r="H119" t="inlineStr"/>
-      <c r="I119" t="inlineStr"/>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>interactive communication style</t>
+        </is>
+      </c>
       <c r="J119" t="inlineStr"/>
       <c r="K119" t="inlineStr">
         <is>
-          <t>A communication that involves altering the area of greatest attention during the delivery of information.</t>
-        </is>
-      </c>
-      <c r="N119" t="inlineStr"/>
-      <c r="O119" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
+          <t>A communication style characterised by being responsive to the recipient's activity.</t>
+        </is>
+      </c>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="N119" t="inlineStr">
+        <is>
+          <t>interactive presentation</t>
         </is>
       </c>
       <c r="P119" t="inlineStr"/>
@@ -4517,73 +4575,73 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>BCIO:044009</t>
+          <t>BCIO:044079</t>
         </is>
       </c>
       <c r="B120" t="inlineStr"/>
       <c r="C120" t="inlineStr"/>
       <c r="D120" t="inlineStr"/>
       <c r="E120" t="inlineStr"/>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>active listening</t>
-        </is>
-      </c>
+      <c r="F120" t="inlineStr"/>
       <c r="G120" t="inlineStr"/>
       <c r="H120" t="inlineStr"/>
-      <c r="I120" t="inlineStr"/>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>active participation encouraging communication style</t>
+        </is>
+      </c>
       <c r="J120" t="inlineStr"/>
       <c r="K120" t="inlineStr">
         <is>
-          <t>A communication involving one participant paying close attention to what is said by another, asking questions and reflecting as needed, in an attempt to fully understand what has been said.</t>
+          <t>A communication style marked by fostering the involvement of the recipient as an engaged actor in the activity to be undertaken rather than as a passive recipient.</t>
+        </is>
+      </c>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
         </is>
       </c>
       <c r="N120" t="inlineStr"/>
-      <c r="O120" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
       <c r="P120" t="inlineStr"/>
       <c r="Q120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>BCIO:044050</t>
+          <t>BCIO:044094</t>
         </is>
       </c>
       <c r="B121" t="inlineStr"/>
       <c r="C121" t="inlineStr"/>
       <c r="D121" t="inlineStr"/>
       <c r="E121" t="inlineStr"/>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>communication using particular language</t>
-        </is>
-      </c>
+      <c r="F121" t="inlineStr"/>
       <c r="G121" t="inlineStr"/>
       <c r="H121" t="inlineStr"/>
-      <c r="I121" t="inlineStr"/>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>communication style conveying support for change</t>
+        </is>
+      </c>
       <c r="J121" t="inlineStr"/>
       <c r="K121" t="inlineStr">
         <is>
-          <t>A communication using certain vocabulary or phraseology.</t>
+          <t>A communication style which imparts one's belief that the recipient can change.</t>
+        </is>
+      </c>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
         </is>
       </c>
       <c r="N121" t="inlineStr"/>
-      <c r="O121" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
       <c r="P121" t="inlineStr"/>
       <c r="Q121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>BCIO:044056</t>
+          <t>BCIO:050392</t>
         </is>
       </c>
       <c r="B122" t="inlineStr"/>
@@ -4591,32 +4649,32 @@
       <c r="D122" t="inlineStr"/>
       <c r="E122" t="inlineStr"/>
       <c r="F122" t="inlineStr"/>
-      <c r="G122" t="inlineStr">
-        <is>
-          <t>communication using selected words from a second language</t>
-        </is>
-      </c>
+      <c r="G122" t="inlineStr"/>
       <c r="H122" t="inlineStr"/>
-      <c r="I122" t="inlineStr"/>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>rushed communication style</t>
+        </is>
+      </c>
       <c r="J122" t="inlineStr"/>
       <c r="K122" t="inlineStr">
         <is>
-          <t>A communication using occasional words chosen from a language spoken by both the instigator and the recipient that is not the main language.</t>
+          <t>A communication style conveying information in a hurried way.</t>
+        </is>
+      </c>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
         </is>
       </c>
       <c r="N122" t="inlineStr"/>
-      <c r="O122" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
       <c r="P122" t="inlineStr"/>
       <c r="Q122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>BCIO:044051</t>
+          <t>BCIO:044091</t>
         </is>
       </c>
       <c r="B123" t="inlineStr"/>
@@ -4624,32 +4682,36 @@
       <c r="D123" t="inlineStr"/>
       <c r="E123" t="inlineStr"/>
       <c r="F123" t="inlineStr"/>
-      <c r="G123" t="inlineStr">
-        <is>
-          <t>communication using neutral language</t>
-        </is>
-      </c>
+      <c r="G123" t="inlineStr"/>
       <c r="H123" t="inlineStr"/>
-      <c r="I123" t="inlineStr"/>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>communication style conveying hopefulness</t>
+        </is>
+      </c>
       <c r="J123" t="inlineStr"/>
       <c r="K123" t="inlineStr">
         <is>
-          <t>A communication using language in a manner which does not demonstrate an opinion on a particular issue.</t>
+          <t>A communication style which imparts a feeling of optimism that a person will attain a desired outcome.</t>
+        </is>
+      </c>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
         </is>
       </c>
       <c r="N123" t="inlineStr"/>
-      <c r="O123" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="P123" t="inlineStr"/>
+      <c r="P123" t="inlineStr">
+        <is>
+          <t>optimism, positivity</t>
+        </is>
+      </c>
       <c r="Q123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>BCIO:044055</t>
+          <t>BCIO:044092</t>
         </is>
       </c>
       <c r="B124" t="inlineStr"/>
@@ -4657,32 +4719,32 @@
       <c r="D124" t="inlineStr"/>
       <c r="E124" t="inlineStr"/>
       <c r="F124" t="inlineStr"/>
-      <c r="G124" t="inlineStr">
-        <is>
-          <t>communication avoiding offensive language</t>
-        </is>
-      </c>
+      <c r="G124" t="inlineStr"/>
       <c r="H124" t="inlineStr"/>
-      <c r="I124" t="inlineStr"/>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>communication style conveying perceived superiority</t>
+        </is>
+      </c>
       <c r="J124" t="inlineStr"/>
       <c r="K124" t="inlineStr">
         <is>
-          <t>A communication using language chosen by the instigator to avoid using words or phrases that could be perceived as rude or insulting.</t>
+          <t>A communication style which imparts a feeling that the instigator believes themselves to be higher in status than the recipient.</t>
+        </is>
+      </c>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
         </is>
       </c>
       <c r="N124" t="inlineStr"/>
-      <c r="O124" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
       <c r="P124" t="inlineStr"/>
       <c r="Q124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>BCIO:044053</t>
+          <t>BCIO:044097</t>
         </is>
       </c>
       <c r="B125" t="inlineStr"/>
@@ -4690,32 +4752,32 @@
       <c r="D125" t="inlineStr"/>
       <c r="E125" t="inlineStr"/>
       <c r="F125" t="inlineStr"/>
-      <c r="G125" t="inlineStr">
-        <is>
-          <t>communication using slang</t>
-        </is>
-      </c>
+      <c r="G125" t="inlineStr"/>
       <c r="H125" t="inlineStr"/>
-      <c r="I125" t="inlineStr"/>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>conversational communication style</t>
+        </is>
+      </c>
       <c r="J125" t="inlineStr"/>
       <c r="K125" t="inlineStr">
         <is>
-          <t>A communication using informal language shared by members of a particular community.</t>
+          <t>A communication style that is typical of interpersonal dialogue which encourages an interactive exchange of ideas and beliefs.</t>
+        </is>
+      </c>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
         </is>
       </c>
       <c r="N125" t="inlineStr"/>
-      <c r="O125" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
       <c r="P125" t="inlineStr"/>
       <c r="Q125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>BCIO:044054</t>
+          <t>BCIO:050380</t>
         </is>
       </c>
       <c r="B126" t="inlineStr"/>
@@ -4723,36 +4785,32 @@
       <c r="D126" t="inlineStr"/>
       <c r="E126" t="inlineStr"/>
       <c r="F126" t="inlineStr"/>
-      <c r="G126" t="inlineStr">
-        <is>
-          <t>communication using specialist language</t>
-        </is>
-      </c>
+      <c r="G126" t="inlineStr"/>
       <c r="H126" t="inlineStr"/>
-      <c r="I126" t="inlineStr"/>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>aggressive communication style</t>
+        </is>
+      </c>
       <c r="J126" t="inlineStr"/>
       <c r="K126" t="inlineStr">
         <is>
-          <t>A communication using words or expressions used by a profession or group that are difficult for others not in that profession or group to understand.</t>
-        </is>
-      </c>
-      <c r="N126" t="inlineStr">
-        <is>
-          <t>using jargon</t>
-        </is>
-      </c>
-      <c r="O126" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
+          <t>A communication style characterised by aggression.</t>
+        </is>
+      </c>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="N126" t="inlineStr"/>
       <c r="P126" t="inlineStr"/>
       <c r="Q126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>BCIO:044052</t>
+          <t>BCIO:044000</t>
         </is>
       </c>
       <c r="B127" t="inlineStr"/>
@@ -4760,23 +4818,28 @@
       <c r="D127" t="inlineStr"/>
       <c r="E127" t="inlineStr"/>
       <c r="F127" t="inlineStr"/>
-      <c r="G127" t="inlineStr">
-        <is>
-          <t>communication using non-pressurising language</t>
-        </is>
-      </c>
+      <c r="G127" t="inlineStr"/>
       <c r="H127" t="inlineStr"/>
-      <c r="I127" t="inlineStr"/>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>behaviour change intervention style of delivery</t>
+        </is>
+      </c>
       <c r="J127" t="inlineStr"/>
       <c r="K127" t="inlineStr">
         <is>
-          <t>A communication using language chosen to avoid coercing or persuading the recipient to think, feel or behave in a certain manner.</t>
+          <t>A communication style that is an attribute of a BCI content communication process.</t>
+        </is>
+      </c>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
         </is>
       </c>
       <c r="N127" t="inlineStr"/>
       <c r="O127" t="inlineStr">
         <is>
-          <t>style of delivery</t>
+          <t>when a communication style is used as part of a BCI content communication process, then it qualifies as a BCI style of delivery</t>
         </is>
       </c>
       <c r="P127" t="inlineStr"/>
@@ -4785,36 +4848,40 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>BCIO:044017</t>
+          <t>BCIO:044117</t>
         </is>
       </c>
       <c r="B128" t="inlineStr"/>
       <c r="C128" t="inlineStr"/>
       <c r="D128" t="inlineStr"/>
       <c r="E128" t="inlineStr"/>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t>banter</t>
-        </is>
-      </c>
+      <c r="F128" t="inlineStr"/>
       <c r="G128" t="inlineStr"/>
       <c r="H128" t="inlineStr"/>
-      <c r="I128" t="inlineStr"/>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>respectful communication style</t>
+        </is>
+      </c>
       <c r="J128" t="inlineStr"/>
       <c r="K128" t="inlineStr">
         <is>
-          <t>A communication involving the exchange of light and teasing remarks intended to be playful.</t>
+          <t>A communication style suggesting an understanding of and regard for the feelings, wishes, or rights of others.</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>Note that teasing is an essential part of the definition of banter. For amusing or enjoyable communication, but without the element of teasing, using entertaining or humourous communication style. Also, note that banter may not always be perceived as playful by the subject of the remarks</t>
-        </is>
-      </c>
-      <c r="N128" t="inlineStr"/>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="N128" t="inlineStr">
+        <is>
+          <t>"acknowledging the victim's feelings"</t>
+        </is>
+      </c>
       <c r="O128" t="inlineStr">
         <is>
-          <t>style of delivery</t>
+          <t>This class involves showing regard for the feelings etc of others from the outset, but not necessarily adapting one's own communication based on what the other says.  In contrast, responsive communication style is adapting the response as a result of how another person is communicating.</t>
         </is>
       </c>
       <c r="P128" t="inlineStr"/>
@@ -4823,78 +4890,73 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>BCIO:044028</t>
+          <t>BCIO:044131</t>
         </is>
       </c>
       <c r="B129" t="inlineStr"/>
       <c r="C129" t="inlineStr"/>
       <c r="D129" t="inlineStr"/>
       <c r="E129" t="inlineStr"/>
-      <c r="F129" t="inlineStr">
-        <is>
-          <t>communication encouraging discussion</t>
-        </is>
-      </c>
+      <c r="F129" t="inlineStr"/>
       <c r="G129" t="inlineStr"/>
       <c r="H129" t="inlineStr"/>
-      <c r="I129" t="inlineStr"/>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>anxious communication style</t>
+        </is>
+      </c>
       <c r="J129" t="inlineStr"/>
       <c r="K129" t="inlineStr">
         <is>
-          <t>A communication in which the initiator promotes an extended two-way discussion regarding a topic.</t>
+          <t>A communication style characterised by nervousness or unease.</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>Contrasts with a more one-way, didactic style</t>
+          <t>style of delivery</t>
         </is>
       </c>
       <c r="N129" t="inlineStr"/>
-      <c r="O129" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
       <c r="P129" t="inlineStr"/>
       <c r="Q129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>BCIO:050388</t>
+          <t>BCIO:050381</t>
         </is>
       </c>
       <c r="B130" t="inlineStr"/>
       <c r="C130" t="inlineStr"/>
       <c r="D130" t="inlineStr"/>
       <c r="E130" t="inlineStr"/>
-      <c r="F130" t="inlineStr">
-        <is>
-          <t>communication showing acknowledgement</t>
-        </is>
-      </c>
+      <c r="F130" t="inlineStr"/>
       <c r="G130" t="inlineStr"/>
       <c r="H130" t="inlineStr"/>
-      <c r="I130" t="inlineStr"/>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>angry communication style</t>
+        </is>
+      </c>
       <c r="J130" t="inlineStr"/>
       <c r="K130" t="inlineStr">
         <is>
-          <t>A communication involving the expressed recognition of what another has expressed.</t>
+          <t>A communication style characterised by anger.</t>
+        </is>
+      </c>
+      <c r="L130" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
         </is>
       </c>
       <c r="N130" t="inlineStr"/>
-      <c r="O130" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
       <c r="P130" t="inlineStr"/>
       <c r="Q130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>BCIO:044021</t>
+          <t>BCIO:044102</t>
         </is>
       </c>
       <c r="B131" t="inlineStr"/>
@@ -4902,107 +4964,102 @@
       <c r="D131" t="inlineStr"/>
       <c r="E131" t="inlineStr"/>
       <c r="F131" t="inlineStr"/>
-      <c r="G131" t="inlineStr">
-        <is>
-          <t>communication acknowledging difficulties</t>
-        </is>
-      </c>
+      <c r="G131" t="inlineStr"/>
       <c r="H131" t="inlineStr"/>
-      <c r="I131" t="inlineStr"/>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>engaging communication style</t>
+        </is>
+      </c>
       <c r="J131" t="inlineStr"/>
       <c r="K131" t="inlineStr">
         <is>
-          <t>A communication showing acknolwedgement conveying empathy or compassion towards a sub-optimal situation or concerns of a recipient.</t>
+          <t>A communication style characterised by attempting to attract and maintain a recipient's interest or attention.</t>
+        </is>
+      </c>
+      <c r="L131" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
         </is>
       </c>
       <c r="N131" t="inlineStr"/>
-      <c r="O131" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
       <c r="P131" t="inlineStr"/>
       <c r="Q131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>BCIO:044069</t>
+          <t>BCIO:044082</t>
         </is>
       </c>
       <c r="B132" t="inlineStr"/>
       <c r="C132" t="inlineStr"/>
       <c r="D132" t="inlineStr"/>
       <c r="E132" t="inlineStr"/>
-      <c r="F132" t="inlineStr">
-        <is>
-          <t>offering reassurance</t>
-        </is>
-      </c>
+      <c r="F132" t="inlineStr"/>
       <c r="G132" t="inlineStr"/>
       <c r="H132" t="inlineStr"/>
-      <c r="I132" t="inlineStr"/>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>articulate communication style</t>
+        </is>
+      </c>
       <c r="J132" t="inlineStr"/>
       <c r="K132" t="inlineStr">
         <is>
-          <t>A communication intended to provide hope and strength in times of anxiety, worry, confusion, grief, distress, or suffering.</t>
+          <t>A communication style characterised by the initiator fluently using language to express ideas.</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>based on Roter Interactional Analysis System</t>
+          <t>style of delivery</t>
         </is>
       </c>
       <c r="N132" t="inlineStr"/>
-      <c r="O132" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="P132" t="inlineStr"/>
-      <c r="Q132" t="inlineStr">
-        <is>
-          <t>made reassuring statements</t>
-        </is>
-      </c>
+      <c r="P132" t="inlineStr">
+        <is>
+          <t>fluent</t>
+        </is>
+      </c>
+      <c r="Q132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>BCIO:044012</t>
+          <t>BCIO:044105</t>
         </is>
       </c>
       <c r="B133" t="inlineStr"/>
       <c r="C133" t="inlineStr"/>
       <c r="D133" t="inlineStr"/>
       <c r="E133" t="inlineStr"/>
-      <c r="F133" t="inlineStr">
-        <is>
-          <t>asking questions</t>
-        </is>
-      </c>
+      <c r="F133" t="inlineStr"/>
       <c r="G133" t="inlineStr"/>
       <c r="H133" t="inlineStr"/>
-      <c r="I133" t="inlineStr"/>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>impatient communication style</t>
+        </is>
+      </c>
       <c r="J133" t="inlineStr"/>
       <c r="K133" t="inlineStr">
         <is>
-          <t>A communication in which some participant requests information from another participant.</t>
+          <t>A communication style conveying feelings of annoyance at time taken to understand or complete a process.</t>
+        </is>
+      </c>
+      <c r="L133" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
         </is>
       </c>
       <c r="N133" t="inlineStr"/>
-      <c r="O133" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
       <c r="P133" t="inlineStr"/>
       <c r="Q133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>BCIO:044013</t>
+          <t>BCIO:044115</t>
         </is>
       </c>
       <c r="B134" t="inlineStr"/>
@@ -5010,32 +5067,32 @@
       <c r="D134" t="inlineStr"/>
       <c r="E134" t="inlineStr"/>
       <c r="F134" t="inlineStr"/>
-      <c r="G134" t="inlineStr">
-        <is>
-          <t>asking closed-ended questions</t>
-        </is>
-      </c>
+      <c r="G134" t="inlineStr"/>
       <c r="H134" t="inlineStr"/>
-      <c r="I134" t="inlineStr"/>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>polite communication style</t>
+        </is>
+      </c>
       <c r="J134" t="inlineStr"/>
       <c r="K134" t="inlineStr">
         <is>
-          <t>Asking questions that can only be answered with a limited set of responses.</t>
+          <t>A communication style characterised by courtesy.</t>
+        </is>
+      </c>
+      <c r="L134" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
         </is>
       </c>
       <c r="N134" t="inlineStr"/>
-      <c r="O134" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
       <c r="P134" t="inlineStr"/>
       <c r="Q134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>BCIO:050382</t>
+          <t>BCIO:044085</t>
         </is>
       </c>
       <c r="B135" t="inlineStr"/>
@@ -5043,32 +5100,32 @@
       <c r="D135" t="inlineStr"/>
       <c r="E135" t="inlineStr"/>
       <c r="F135" t="inlineStr"/>
-      <c r="G135" t="inlineStr">
-        <is>
-          <t>asking clarifying questions</t>
-        </is>
-      </c>
+      <c r="G135" t="inlineStr"/>
       <c r="H135" t="inlineStr"/>
-      <c r="I135" t="inlineStr"/>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>collaborative communication style</t>
+        </is>
+      </c>
       <c r="J135" t="inlineStr"/>
       <c r="K135" t="inlineStr">
         <is>
-          <t>Asking questions in order to better understand an issue.</t>
+          <t>A communication style characterised by a sense of the initiator and recipient working together, the initiator showing sensitivity to the others' needs, in order to obtain an outcome desired by all.</t>
+        </is>
+      </c>
+      <c r="L135" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
         </is>
       </c>
       <c r="N135" t="inlineStr"/>
-      <c r="O135" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
       <c r="P135" t="inlineStr"/>
       <c r="Q135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>BCIO:044015</t>
+          <t>BCIO:044083</t>
         </is>
       </c>
       <c r="B136" t="inlineStr"/>
@@ -5076,27 +5133,32 @@
       <c r="D136" t="inlineStr"/>
       <c r="E136" t="inlineStr"/>
       <c r="F136" t="inlineStr"/>
-      <c r="G136" t="inlineStr">
-        <is>
-          <t>asking leading questions</t>
-        </is>
-      </c>
+      <c r="G136" t="inlineStr"/>
       <c r="H136" t="inlineStr"/>
-      <c r="I136" t="inlineStr"/>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>attentive communication style</t>
+        </is>
+      </c>
       <c r="J136" t="inlineStr"/>
       <c r="K136" t="inlineStr">
         <is>
-          <t>Asking questions designed to prompt the questionee to answer in a specific, pre-determined manner.</t>
+          <t>A communication style characterised by purposeful consideration of another's statements.</t>
+        </is>
+      </c>
+      <c r="L136" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
         </is>
       </c>
       <c r="N136" t="inlineStr">
         <is>
-          <t>asking directive questions</t>
+          <t>"listened carefully to what you had to say"</t>
         </is>
       </c>
       <c r="O136" t="inlineStr">
         <is>
-          <t>style of delivery</t>
+          <t>This involves communicating in a manner that ensures the recipient knows that they are being heard</t>
         </is>
       </c>
       <c r="P136" t="inlineStr"/>
@@ -5105,7 +5167,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>BCIO:044014</t>
+          <t>BCIO:044095</t>
         </is>
       </c>
       <c r="B137" t="inlineStr"/>
@@ -5113,32 +5175,32 @@
       <c r="D137" t="inlineStr"/>
       <c r="E137" t="inlineStr"/>
       <c r="F137" t="inlineStr"/>
-      <c r="G137" t="inlineStr">
-        <is>
-          <t>asking focused questions</t>
-        </is>
-      </c>
+      <c r="G137" t="inlineStr"/>
       <c r="H137" t="inlineStr"/>
-      <c r="I137" t="inlineStr"/>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>communication style demonstrating positive regard</t>
+        </is>
+      </c>
       <c r="J137" t="inlineStr"/>
       <c r="K137" t="inlineStr">
         <is>
-          <t>Asking questions designed to narrow discussion to focus on a particular aspect or topic.</t>
+          <t>A communication style demonstrating acceptance of everything about the recipient.</t>
+        </is>
+      </c>
+      <c r="L137" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
         </is>
       </c>
       <c r="N137" t="inlineStr"/>
-      <c r="O137" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
       <c r="P137" t="inlineStr"/>
       <c r="Q137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>BCIO:044016</t>
+          <t>BCIO:044098</t>
         </is>
       </c>
       <c r="B138" t="inlineStr"/>
@@ -5146,23 +5208,27 @@
       <c r="D138" t="inlineStr"/>
       <c r="E138" t="inlineStr"/>
       <c r="F138" t="inlineStr"/>
-      <c r="G138" t="inlineStr">
-        <is>
-          <t>asking open-ended questions</t>
-        </is>
-      </c>
+      <c r="G138" t="inlineStr"/>
       <c r="H138" t="inlineStr"/>
-      <c r="I138" t="inlineStr"/>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>didactic communication style</t>
+        </is>
+      </c>
       <c r="J138" t="inlineStr"/>
       <c r="K138" t="inlineStr">
         <is>
-          <t>Asking questions that cannot be answered with a simple yes or no, but instead require the questionee to elaborate on their points.</t>
-        </is>
-      </c>
-      <c r="N138" t="inlineStr"/>
-      <c r="O138" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
+          <t>A communication style characterised by the initiator addressing the recipient in the manner of a teacher or lecturer.</t>
+        </is>
+      </c>
+      <c r="L138" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="N138" t="inlineStr">
+        <is>
+          <t>gave a short lecture, conference presentation</t>
         </is>
       </c>
       <c r="P138" t="inlineStr"/>
@@ -5171,45 +5237,49 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>BCIO:044019</t>
+          <t>BCIO:044120</t>
         </is>
       </c>
       <c r="B139" t="inlineStr"/>
       <c r="C139" t="inlineStr"/>
       <c r="D139" t="inlineStr"/>
       <c r="E139" t="inlineStr"/>
-      <c r="F139" t="inlineStr">
-        <is>
-          <t>discussion</t>
-        </is>
-      </c>
+      <c r="F139" t="inlineStr"/>
       <c r="G139" t="inlineStr"/>
       <c r="H139" t="inlineStr"/>
-      <c r="I139" t="inlineStr"/>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>structured communication style</t>
+        </is>
+      </c>
       <c r="J139" t="inlineStr"/>
       <c r="K139" t="inlineStr">
         <is>
-          <t>A communication involving an extended exchange of utterances between an instigator and at least one other person.</t>
+          <t>A communication style involving the communication content having constituent pre-planned parts.</t>
         </is>
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t>An utterance is an uninterrupted stretch of speech or writing produced by an individual on a particular occasion. An utterance can range from a single word to a complete sentence.</t>
+          <t>style of delivery</t>
         </is>
       </c>
       <c r="N139" t="inlineStr"/>
       <c r="O139" t="inlineStr">
         <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="P139" t="inlineStr"/>
+          <t>This class is pre-planned style but not to the extent of using a written script. In contrast, "Script-based communication" involves tightly following a set of written instructions.</t>
+        </is>
+      </c>
+      <c r="P139" t="inlineStr">
+        <is>
+          <t>standardised</t>
+        </is>
+      </c>
       <c r="Q139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>BCIO:044020</t>
+          <t>BCIO:044110</t>
         </is>
       </c>
       <c r="B140" t="inlineStr"/>
@@ -5217,98 +5287,102 @@
       <c r="D140" t="inlineStr"/>
       <c r="E140" t="inlineStr"/>
       <c r="F140" t="inlineStr"/>
-      <c r="G140" t="inlineStr">
-        <is>
-          <t>classroom-style discussion</t>
-        </is>
-      </c>
+      <c r="G140" t="inlineStr"/>
       <c r="H140" t="inlineStr"/>
-      <c r="I140" t="inlineStr"/>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>non-defensive communication style</t>
+        </is>
+      </c>
       <c r="J140" t="inlineStr"/>
       <c r="K140" t="inlineStr">
         <is>
-          <t>A discussion led by the initiator in a manner typical of a teacher or lecturer.</t>
+          <t>A communication style characterised by suggesting the initiator is open to or able to accept criticism.</t>
+        </is>
+      </c>
+      <c r="L140" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
         </is>
       </c>
       <c r="N140" t="inlineStr"/>
-      <c r="O140" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
       <c r="P140" t="inlineStr"/>
       <c r="Q140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>BCIO:044024</t>
+          <t>BCIO:044086</t>
         </is>
       </c>
       <c r="B141" t="inlineStr"/>
       <c r="C141" t="inlineStr"/>
       <c r="D141" t="inlineStr"/>
       <c r="E141" t="inlineStr"/>
-      <c r="F141" t="inlineStr">
-        <is>
-          <t>communication avoiding argumentation</t>
-        </is>
-      </c>
+      <c r="F141" t="inlineStr"/>
       <c r="G141" t="inlineStr"/>
       <c r="H141" t="inlineStr"/>
-      <c r="I141" t="inlineStr"/>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>cold communication style</t>
+        </is>
+      </c>
       <c r="J141" t="inlineStr"/>
       <c r="K141" t="inlineStr">
         <is>
-          <t>A communication which aims to focus on the feelings of others without debating the truth or falsity of statements or ideas.</t>
+          <t>A communication style suggesting a lack of human interest or friendliness towards the recipient.</t>
+        </is>
+      </c>
+      <c r="L141" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
         </is>
       </c>
       <c r="N141" t="inlineStr"/>
-      <c r="O141" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
       <c r="P141" t="inlineStr"/>
       <c r="Q141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>BCIO:044071</t>
+          <t>BCIO:044090</t>
         </is>
       </c>
       <c r="B142" t="inlineStr"/>
       <c r="C142" t="inlineStr"/>
       <c r="D142" t="inlineStr"/>
       <c r="E142" t="inlineStr"/>
-      <c r="F142" t="inlineStr">
-        <is>
-          <t>reflective communication</t>
-        </is>
-      </c>
+      <c r="F142" t="inlineStr"/>
       <c r="G142" t="inlineStr"/>
       <c r="H142" t="inlineStr"/>
-      <c r="I142" t="inlineStr"/>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>communication style conveying genuineness</t>
+        </is>
+      </c>
       <c r="J142" t="inlineStr"/>
       <c r="K142" t="inlineStr">
         <is>
-          <t>A communication presenting a person's previously expressed thoughts and feelings back to them.</t>
+          <t>A communication style which suggests one is acting in line with one's true values and beliefs.</t>
+        </is>
+      </c>
+      <c r="L142" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
         </is>
       </c>
       <c r="N142" t="inlineStr"/>
-      <c r="O142" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="P142" t="inlineStr"/>
+      <c r="P142" t="inlineStr">
+        <is>
+          <t>sincerity</t>
+        </is>
+      </c>
       <c r="Q142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>BCIO:044074</t>
+          <t>BCIO:050389</t>
         </is>
       </c>
       <c r="B143" t="inlineStr"/>
@@ -5316,27 +5390,28 @@
       <c r="D143" t="inlineStr"/>
       <c r="E143" t="inlineStr"/>
       <c r="F143" t="inlineStr"/>
-      <c r="G143" t="inlineStr">
-        <is>
-          <t>metaphor-using reflective communication</t>
-        </is>
-      </c>
+      <c r="G143" t="inlineStr"/>
       <c r="H143" t="inlineStr"/>
-      <c r="I143" t="inlineStr"/>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>direct communication style</t>
+        </is>
+      </c>
       <c r="J143" t="inlineStr"/>
       <c r="K143" t="inlineStr">
         <is>
-          <t>A reflective communication in which the instigator  replaces a word or phrase of the recipient's prior assertion with a figure of speech suggesting an analogy.</t>
-        </is>
-      </c>
-      <c r="N143" t="inlineStr">
-        <is>
-          <t>"metaphorical reflection" in Motivational Interviewing</t>
-        </is>
-      </c>
+          <t>A communication style characterised by the explicit presentation of information.</t>
+        </is>
+      </c>
+      <c r="L143" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="N143" t="inlineStr"/>
       <c r="O143" t="inlineStr">
         <is>
-          <t>style of delivery</t>
+          <t>Note that this class is different from directive communication style</t>
         </is>
       </c>
       <c r="P143" t="inlineStr"/>
@@ -5345,7 +5420,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>BCIO:044073</t>
+          <t>BCIO:044121</t>
         </is>
       </c>
       <c r="B144" t="inlineStr"/>
@@ -5353,36 +5428,32 @@
       <c r="D144" t="inlineStr"/>
       <c r="E144" t="inlineStr"/>
       <c r="F144" t="inlineStr"/>
-      <c r="G144" t="inlineStr">
-        <is>
-          <t>double-sided reflective communication</t>
-        </is>
-      </c>
+      <c r="G144" t="inlineStr"/>
       <c r="H144" t="inlineStr"/>
-      <c r="I144" t="inlineStr"/>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>theatrical communication style</t>
+        </is>
+      </c>
       <c r="J144" t="inlineStr"/>
       <c r="K144" t="inlineStr">
         <is>
-          <t>A reflective communication in which the instigator aims to highlight both the positive and negative sides of an issue as previously expressed by the recipient.</t>
-        </is>
-      </c>
-      <c r="N144" t="inlineStr">
-        <is>
-          <t>"double-sided reflection" in Motivational Interviewing</t>
-        </is>
-      </c>
-      <c r="O144" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
+          <t>A communication style similar to that used for dramatic performance or the theatre.</t>
+        </is>
+      </c>
+      <c r="L144" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="N144" t="inlineStr"/>
       <c r="P144" t="inlineStr"/>
       <c r="Q144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>BCIO:044075</t>
+          <t>BCIO:044126</t>
         </is>
       </c>
       <c r="B145" t="inlineStr"/>
@@ -5390,36 +5461,32 @@
       <c r="D145" t="inlineStr"/>
       <c r="E145" t="inlineStr"/>
       <c r="F145" t="inlineStr"/>
-      <c r="G145" t="inlineStr">
-        <is>
-          <t>emotion-emphasising reflective communication</t>
-        </is>
-      </c>
-      <c r="H145" t="inlineStr"/>
+      <c r="G145" t="inlineStr"/>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>oral communication pace</t>
+        </is>
+      </c>
       <c r="I145" t="inlineStr"/>
       <c r="J145" t="inlineStr"/>
       <c r="K145" t="inlineStr">
         <is>
-          <t>A reflective communication highlighting the emotional aspects of an issue as previously described by the recipient.</t>
-        </is>
-      </c>
-      <c r="N145" t="inlineStr">
-        <is>
-          <t>"reflection of feeling" in Motivational Interviewing</t>
-        </is>
-      </c>
-      <c r="O145" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
+          <t>An attribute of an oral communication relating to the speed with which an individual speaks.</t>
+        </is>
+      </c>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="N145" t="inlineStr"/>
       <c r="P145" t="inlineStr"/>
       <c r="Q145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>BCIO:044072</t>
+          <t>BCIO:044125</t>
         </is>
       </c>
       <c r="B146" t="inlineStr"/>
@@ -5427,36 +5494,32 @@
       <c r="D146" t="inlineStr"/>
       <c r="E146" t="inlineStr"/>
       <c r="F146" t="inlineStr"/>
-      <c r="G146" t="inlineStr">
-        <is>
-          <t>summarising reflective communication</t>
-        </is>
-      </c>
-      <c r="H146" t="inlineStr"/>
+      <c r="G146" t="inlineStr"/>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>tone of voice</t>
+        </is>
+      </c>
       <c r="I146" t="inlineStr"/>
       <c r="J146" t="inlineStr"/>
       <c r="K146" t="inlineStr">
         <is>
-          <t>A reflective communication in which the instigator pulls together key points from a complex story told by the recipient in a succinct restatement.</t>
-        </is>
-      </c>
-      <c r="N146" t="inlineStr">
-        <is>
-          <t>"summarising reflection" in Motivational Interviewing</t>
-        </is>
-      </c>
-      <c r="O146" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
+          <t>An attribute of an oral communication relating to the rhythm and pitch of what is said.</t>
+        </is>
+      </c>
+      <c r="L146" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="N146" t="inlineStr"/>
       <c r="P146" t="inlineStr"/>
       <c r="Q146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>BCIO:044076</t>
+          <t>BCIO:044127</t>
         </is>
       </c>
       <c r="B147" t="inlineStr"/>
@@ -5464,27 +5527,27 @@
       <c r="D147" t="inlineStr"/>
       <c r="E147" t="inlineStr"/>
       <c r="F147" t="inlineStr"/>
-      <c r="G147" t="inlineStr">
-        <is>
-          <t>re-evaluation prompting reflective communication</t>
-        </is>
-      </c>
-      <c r="H147" t="inlineStr"/>
+      <c r="G147" t="inlineStr"/>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>object visual style</t>
+        </is>
+      </c>
       <c r="I147" t="inlineStr"/>
       <c r="J147" t="inlineStr"/>
       <c r="K147" t="inlineStr">
         <is>
-          <t>A reflective communication in which the instigator restates the recipient's prior assertation in a less credible way to prompt reconsideration of the assertion.</t>
+          <t>An attribute of an object used in a communication process, concerning how information sensed with the eyes is presented, which may include colours/fonts/images/spacing/sizing.</t>
+        </is>
+      </c>
+      <c r="L147" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
         </is>
       </c>
       <c r="N147" t="inlineStr">
         <is>
-          <t>"amplified reflection" in Motivational Interviewing</t>
-        </is>
-      </c>
-      <c r="O147" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
+          <t>colour scheme chosen for a website, style of images used for a booklet, brightly coloured reminder stickers</t>
         </is>
       </c>
       <c r="P147" t="inlineStr"/>
@@ -5493,81 +5556,69 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>BCIO:044124</t>
+          <t>BCIO:044130</t>
         </is>
       </c>
       <c r="B148" t="inlineStr"/>
       <c r="C148" t="inlineStr"/>
       <c r="D148" t="inlineStr"/>
       <c r="E148" t="inlineStr"/>
-      <c r="F148" t="inlineStr">
-        <is>
-          <t>relationship building</t>
-        </is>
-      </c>
+      <c r="F148" t="inlineStr"/>
       <c r="G148" t="inlineStr"/>
-      <c r="H148" t="inlineStr"/>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>readability</t>
+        </is>
+      </c>
       <c r="I148" t="inlineStr"/>
       <c r="J148" t="inlineStr"/>
       <c r="K148" t="inlineStr">
         <is>
-          <t>A communication aimed at building or managing aspects of the interpersonal relationship between an initiator and a recipient rather than focusing on delivering communication content.</t>
-        </is>
-      </c>
-      <c r="N148" t="inlineStr"/>
-      <c r="O148" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
+          <t>An attribute of a text used in communication process, concerning the ease of understanding the wording or other qualitative aspects of the text that facilitate comprehension.</t>
+        </is>
+      </c>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="N148" t="inlineStr">
+        <is>
+          <t>including adequate blank space and empty circles for the young people and their carers to record and review agenda items</t>
         </is>
       </c>
       <c r="P148" t="inlineStr"/>
-      <c r="Q148" t="inlineStr">
-        <is>
-          <t>offering contact, inviting patient to contact you in the event of difficulties or questions</t>
-        </is>
-      </c>
+      <c r="Q148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>BCIO:044047</t>
+          <t>OGMS:0000060</t>
         </is>
       </c>
       <c r="B149" t="inlineStr"/>
       <c r="C149" t="inlineStr"/>
       <c r="D149" t="inlineStr"/>
-      <c r="E149" t="inlineStr"/>
-      <c r="F149" t="inlineStr">
-        <is>
-          <t>communication using commands</t>
-        </is>
-      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>bodily process</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr"/>
       <c r="G149" t="inlineStr"/>
       <c r="H149" t="inlineStr"/>
       <c r="I149" t="inlineStr"/>
       <c r="J149" t="inlineStr"/>
       <c r="K149" t="inlineStr">
         <is>
-          <t>A communication using statements that order or direct a person to think or behave in a certain way.</t>
-        </is>
-      </c>
-      <c r="N149" t="inlineStr">
-        <is>
-          <t>communication using imperatives</t>
-        </is>
-      </c>
-      <c r="O149" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="P149" t="inlineStr"/>
-      <c r="Q149" t="inlineStr"/>
+          <t>A &lt;process&gt; in which at least one bodily component of an organism participates.</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>BCIO:044001</t>
+          <t>BCIO:036000</t>
         </is>
       </c>
       <c r="B150" t="inlineStr"/>
@@ -5576,7 +5627,7 @@
       <c r="E150" t="inlineStr"/>
       <c r="F150" t="inlineStr">
         <is>
-          <t>intervention content communication process</t>
+          <t>individual human behaviour</t>
         </is>
       </c>
       <c r="G150" t="inlineStr"/>
@@ -5585,27 +5636,14 @@
       <c r="J150" t="inlineStr"/>
       <c r="K150" t="inlineStr">
         <is>
-          <t>A communication that transmits the content of an intervention</t>
-        </is>
-      </c>
-      <c r="L150" t="inlineStr">
-        <is>
-          <t>Note that an intervention is a planned process with the aim of influencing some outcome whereas a behaviour change intervention is an intervention that aims to influence human behaviour as an outcome.</t>
-        </is>
-      </c>
-      <c r="N150" t="inlineStr"/>
-      <c r="O150" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="P150" t="inlineStr"/>
-      <c r="Q150" t="inlineStr"/>
+          <t>A bodily process of a human that involves co-ordinated contraction of striated muscles controlled by the brain.</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>BCIO:044002</t>
+          <t>BCIO:050457</t>
         </is>
       </c>
       <c r="B151" t="inlineStr"/>
@@ -5615,7 +5653,7 @@
       <c r="F151" t="inlineStr"/>
       <c r="G151" t="inlineStr">
         <is>
-          <t>behaviour change intervention content communication process</t>
+          <t>expressive behaviour</t>
         </is>
       </c>
       <c r="H151" t="inlineStr"/>
@@ -5623,143 +5661,121 @@
       <c r="J151" t="inlineStr"/>
       <c r="K151" t="inlineStr">
         <is>
-          <t>An intervention content communication process that is about behaviour change intervention content</t>
+          <t>An individual human behaviour that conveys a thought or feeling.</t>
         </is>
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>A behaviour change intervention is a planned process that aims to influence human behaviour.  In contrast, an intervention is a planned process with the aim of influencing some outcome.  This outcome may be other than human behaviour.</t>
+          <t>style of delivery</t>
         </is>
       </c>
       <c r="N151" t="inlineStr"/>
-      <c r="O151" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
       <c r="P151" t="inlineStr"/>
       <c r="Q151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>BCIO:044029</t>
+          <t>BCIO:050374</t>
         </is>
       </c>
       <c r="B152" t="inlineStr"/>
       <c r="C152" t="inlineStr"/>
       <c r="D152" t="inlineStr"/>
       <c r="E152" t="inlineStr"/>
-      <c r="F152" t="inlineStr">
-        <is>
-          <t>communication evoking another's ideas about change</t>
-        </is>
-      </c>
+      <c r="F152" t="inlineStr"/>
       <c r="G152" t="inlineStr"/>
-      <c r="H152" t="inlineStr"/>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>laughing</t>
+        </is>
+      </c>
       <c r="I152" t="inlineStr"/>
       <c r="J152" t="inlineStr"/>
       <c r="K152" t="inlineStr">
         <is>
-          <t>A communication in which the initiator attempts to elicit the recipient’s own thoughts and ideas about change rather than imposing the initiator’s own opinion.</t>
-        </is>
-      </c>
-      <c r="N152" t="inlineStr">
-        <is>
-          <t>evoking change talk in motivational interviewing</t>
-        </is>
-      </c>
-      <c r="O152" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
+          <t>An expressive behaviour showing elation, amusement or scorn by means of facial expressions and repeated sharp exhalations.</t>
+        </is>
+      </c>
+      <c r="L152" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="N152" t="inlineStr"/>
       <c r="P152" t="inlineStr"/>
       <c r="Q152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>BCIO:044049</t>
+          <t>BCIO:036034</t>
         </is>
       </c>
       <c r="B153" t="inlineStr"/>
       <c r="C153" t="inlineStr"/>
       <c r="D153" t="inlineStr"/>
       <c r="E153" t="inlineStr"/>
-      <c r="F153" t="inlineStr">
-        <is>
-          <t>communication using interjections to signal attentiveness</t>
-        </is>
-      </c>
+      <c r="F153" t="inlineStr"/>
       <c r="G153" t="inlineStr"/>
-      <c r="H153" t="inlineStr"/>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>human communication behaviour</t>
+        </is>
+      </c>
       <c r="I153" t="inlineStr"/>
       <c r="J153" t="inlineStr"/>
       <c r="K153" t="inlineStr">
         <is>
-          <t>A communication in which one person uses brief interjections to signal that they are listening to what the other person is saying.</t>
+          <t>An expressive behaviour that involves the transmission of information between two or more people.</t>
         </is>
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t>An interjection is a word, phrase or exclamation which is typically unconnected to a sentence and is used to express an emotion or reaction.</t>
-        </is>
-      </c>
-      <c r="N153" t="inlineStr">
-        <is>
-          <t>"Back-channels" or "undertalk" in the Roter Interaction Analysis System</t>
-        </is>
-      </c>
-      <c r="O153" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="N153" t="inlineStr"/>
       <c r="P153" t="inlineStr"/>
-      <c r="Q153" t="inlineStr">
-        <is>
-          <t>Words like "interesting", "yeah"," mmhmm"</t>
-        </is>
-      </c>
+      <c r="Q153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>BCIO:044037</t>
+          <t>BCIO:050237</t>
         </is>
       </c>
       <c r="B154" t="inlineStr"/>
       <c r="C154" t="inlineStr"/>
       <c r="D154" t="inlineStr"/>
       <c r="E154" t="inlineStr"/>
-      <c r="F154" t="inlineStr">
-        <is>
-          <t>communication involving agreement</t>
-        </is>
-      </c>
+      <c r="F154" t="inlineStr"/>
       <c r="G154" t="inlineStr"/>
       <c r="H154" t="inlineStr"/>
-      <c r="I154" t="inlineStr"/>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>linguistic communication behaviour</t>
+        </is>
+      </c>
       <c r="J154" t="inlineStr"/>
       <c r="K154" t="inlineStr">
         <is>
-          <t>A communication in which one participant concurs with the views stated by another.</t>
+          <t>A human communication behaviour in which the information that is communicated is encoded in language.</t>
+        </is>
+      </c>
+      <c r="L154" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
         </is>
       </c>
       <c r="N154" t="inlineStr"/>
-      <c r="O154" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
       <c r="P154" t="inlineStr"/>
       <c r="Q154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>BCIO:044038</t>
+          <t>BCIO:050441</t>
         </is>
       </c>
       <c r="B155" t="inlineStr"/>
@@ -5769,7 +5785,7 @@
       <c r="F155" t="inlineStr"/>
       <c r="G155" t="inlineStr">
         <is>
-          <t>communication involving agreement followed by highlighting incongruent aspects</t>
+          <t>socially-related behaviour</t>
         </is>
       </c>
       <c r="H155" t="inlineStr"/>
@@ -5777,63 +5793,47 @@
       <c r="J155" t="inlineStr"/>
       <c r="K155" t="inlineStr">
         <is>
-          <t>A communication involving agreement in which one participant concurs with the views stated by another and then points out an incongruent aspect of the situation under discussion.</t>
-        </is>
-      </c>
-      <c r="N155" t="inlineStr">
-        <is>
-          <t>"agreement with a twist" in motivational interviewing</t>
-        </is>
-      </c>
-      <c r="O155" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="P155" t="inlineStr"/>
-      <c r="Q155" t="inlineStr"/>
+          <t>An individual human behaviour that relates to the social environment.</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>BCIO:044060</t>
+          <t>BCIO:036025</t>
         </is>
       </c>
       <c r="B156" t="inlineStr"/>
       <c r="C156" t="inlineStr"/>
       <c r="D156" t="inlineStr"/>
       <c r="E156" t="inlineStr"/>
-      <c r="F156" t="inlineStr">
-        <is>
-          <t>guiding communication</t>
-        </is>
-      </c>
+      <c r="F156" t="inlineStr"/>
       <c r="G156" t="inlineStr"/>
-      <c r="H156" t="inlineStr"/>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>inter-personal behaviour</t>
+        </is>
+      </c>
       <c r="I156" t="inlineStr"/>
       <c r="J156" t="inlineStr"/>
       <c r="K156" t="inlineStr">
         <is>
-          <t>A communication that involves suggesting adoption of certain beliefs, theories or lines of action by others.</t>
+          <t>An &lt;socially-related behaviour&gt; that involves an interaction between two or more people.</t>
+        </is>
+      </c>
+      <c r="L156" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
         </is>
       </c>
       <c r="N156" t="inlineStr"/>
-      <c r="O156" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
       <c r="P156" t="inlineStr"/>
-      <c r="Q156" t="inlineStr">
-        <is>
-          <t>When a practitioner suggests to a patient 'Could you think about it like this...'</t>
-        </is>
-      </c>
+      <c r="Q156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>OBI:0000011</t>
+          <t>COB:0000082</t>
         </is>
       </c>
       <c r="B157" t="inlineStr"/>
@@ -5851,7 +5851,7 @@
       <c r="J157" t="inlineStr"/>
       <c r="K157" t="inlineStr">
         <is>
-          <t>A process that realizes a plan which is the concretization of a plan specification.</t>
+          <t>A process that is initiated by an agent who intends to carry out a plan to achieve an objective through one or more actions as described in a plan specification.</t>
         </is>
       </c>
     </row>
@@ -5879,19 +5879,19 @@
           <t>A planned process by which intervention content is delivered.</t>
         </is>
       </c>
+      <c r="L158" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
       <c r="N158" t="inlineStr"/>
-      <c r="O158" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
       <c r="P158" t="inlineStr"/>
       <c r="Q158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>BCIO:044008</t>
+          <t>BCIO:044007</t>
         </is>
       </c>
       <c r="B159" t="inlineStr"/>
@@ -5901,7 +5901,7 @@
       <c r="F159" t="inlineStr"/>
       <c r="G159" t="inlineStr">
         <is>
-          <t>source-led intervention delivery</t>
+          <t>participant-led intervention delivery</t>
         </is>
       </c>
       <c r="H159" t="inlineStr"/>
@@ -5909,15 +5909,15 @@
       <c r="J159" t="inlineStr"/>
       <c r="K159" t="inlineStr">
         <is>
-          <t>An intervention delivery in which the intervention person source takes the lead in determining the focus of the intervention.</t>
+          <t>An intervention delivery in which the participant takes the lead in determining the focus of the intervention.</t>
+        </is>
+      </c>
+      <c r="L159" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
         </is>
       </c>
       <c r="N159" t="inlineStr"/>
-      <c r="O159" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
       <c r="P159" t="inlineStr"/>
       <c r="Q159" t="inlineStr"/>
     </row>
@@ -5945,19 +5945,19 @@
           <t>An intervention delivery characterised by efforts by an intervention source to give a person the resources they need to manage their own life and make them an active participant in deciding how to move forward.</t>
         </is>
       </c>
+      <c r="L160" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
       <c r="N160" t="inlineStr"/>
-      <c r="O160" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
       <c r="P160" t="inlineStr"/>
       <c r="Q160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>BCIO:044007</t>
+          <t>BCIO:044008</t>
         </is>
       </c>
       <c r="B161" t="inlineStr"/>
@@ -5967,7 +5967,7 @@
       <c r="F161" t="inlineStr"/>
       <c r="G161" t="inlineStr">
         <is>
-          <t>participant-led intervention delivery</t>
+          <t>source-led intervention delivery</t>
         </is>
       </c>
       <c r="H161" t="inlineStr"/>
@@ -5975,15 +5975,15 @@
       <c r="J161" t="inlineStr"/>
       <c r="K161" t="inlineStr">
         <is>
-          <t>An intervention delivery in which the participant takes the lead in determining the focus of the intervention.</t>
+          <t>An intervention delivery in which the intervention person source takes the lead in determining the focus of the intervention.</t>
+        </is>
+      </c>
+      <c r="L161" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
         </is>
       </c>
       <c r="N161" t="inlineStr"/>
-      <c r="O161" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
       <c r="P161" t="inlineStr"/>
       <c r="Q161" t="inlineStr"/>
     </row>
@@ -6011,12 +6011,12 @@
           <t>An intervention delivery in which the intervention is a behaviour change intervention.</t>
         </is>
       </c>
+      <c r="L162" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
       <c r="N162" t="inlineStr"/>
-      <c r="O162" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
       <c r="P162" t="inlineStr"/>
       <c r="Q162" t="inlineStr"/>
     </row>
